--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:AA91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
@@ -452,120 +452,142 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Kombi</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Uebung</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Muskel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Equipment_default</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Haende</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Griff</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ebene</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Griffweite</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Kabel_Hoehe</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Stand_deg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Bank_Kabel</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Koerper_Bank</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Koerper_Pos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Discriminant_Dim</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>primary_motion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shoulder_elv_start</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shoulder_elv_end</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>shoulder_elv_fix</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>elbow_flex_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elbow_flex_end</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>elbow_flex_fix</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>elv_angle_override</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>shoulder_rot_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>shoulder_rot_end</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>shoulder_rot_fix</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Notizen</t>
         </is>
@@ -574,1785 +596,2319 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pushdown (l-s)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>pushdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>EZ bend</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>n-p</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>l-s</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>16-22</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>110</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pushdown (lat)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>extension (lat)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EZ bend</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>nooses</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>n-p</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>16-22</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>extension (l-s)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>extension (sag)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>nooses</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>sup/s-n/n/n-p/pro</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>l-s</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>16-22</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>extension (lat)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>overhead extension (l-s)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>nooses</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>sup/s-n/n/n-p/pro</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>16-22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0/90</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>l-s</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9-15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>165</v>
+      </c>
+      <c r="T5" t="n">
+        <v>140</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>extension (sag)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>overhead extension (lat)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>nooses</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>d-handle var</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sup/s-n/n/n-p/pro</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>16-22</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>s-n/n/n-p</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9-15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>90/180</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>165</v>
+      </c>
+      <c r="T6" t="n">
+        <v>140</v>
+      </c>
+      <c r="U6" t="n">
+        <v>10</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overhead extension</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>overhead extension (sag)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>triceps</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dumbell</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>n-p</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>x0.5</t>
+          <t>sag</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>upright</t>
+          <t>9-15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>90/180</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>165</v>
+      </c>
+      <c r="T7" t="n">
+        <v>140</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>overhead extension (l-s)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>triceps</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nooses</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sup/s-n/n/n-p/pro</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>l-s</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>9-15</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>s-t/trans</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1-8/9-15/16-22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>90/90os</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>80</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>20</v>
+      </c>
       <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overhead extension (lat)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>triceps</t>
+          <t>lateral raise</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>d-handle var</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>s-n/n/n-p</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
+          <t>n/n-p</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>9-15</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>90/180</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1-8/9-15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>80</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>10</v>
+      </c>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overhead extension (sag)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>triceps</t>
+          <t>front row</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>d-handle var</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>nooses</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sup/s-n/n/n-p/pro</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>9-15</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>90/180</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0/180</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>80</v>
+      </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>90</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fly (s-t/trans)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>archer pull</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>d-handle var</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sup</t>
-        </is>
-      </c>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>s-t/trans</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1-8/9-15/16-22</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>90/90os</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>trans</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>plane</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>60</v>
+      </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>120</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fly (t-l)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>front raise</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>d-handle fix</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>d-handle var</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sup</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>t-l</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>1-8</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0/180</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>90</v>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>10</v>
+      </c>
       <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fly (trans)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>d-handle fix</t>
+          <t>biceps</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>EZ bend</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sup/s-n</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>s-n/n-p</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>9-15</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="n">
+        <v>145</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fly (trans/t-l)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>curl (sag)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dumbell</t>
+          <t>biceps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>EZ bend</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>trans/t-l</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>flat/incl</t>
+          <t>1-8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>145</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lateral raise</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>Bayesian curl</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dumbell</t>
+          <t>biceps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>n/n-p</t>
-        </is>
-      </c>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>sitting</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>145</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lateral raise (1-8/9-15)</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>crossbody curl</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>d-handle var</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>n/n-p</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1-8/9-15</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>90/90os</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
+        <v>145</v>
+      </c>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>front row</t>
+          <t>Free + Cable</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>face pull</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>nooses</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>n/n-p/pro</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>1-8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0/180</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>90</v>
+      </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>90</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>archer pull (1-8)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>skull crusher (s-t)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nose bar</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>trans</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>s-t</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>x0.5/x1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>flat/incl</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="n">
+        <v>140</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>archer pull (9-15)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>skull crusher (sag)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>nose bar</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>n/n-p/pro</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>trans</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9-15</t>
+          <t>x0.5/x1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>flat/incl</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>90/135</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>90</v>
+      </c>
+      <c r="T19" t="n">
+        <v>140</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>front raise</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>overhead extension</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>s-n/n/n-p/pro</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+          <t>n-p</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>x0.5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>upright</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>lying</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>sitting</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>165</v>
+      </c>
+      <c r="T20" t="n">
+        <v>140</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>front raise (1-8)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>overhead extension (l-s)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>d-handle var</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>ez bar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>sup/s-n/n/n-p/pro</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>l-s</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>x0.5/x1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0/180</t>
+          <t>upright</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>cable_h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>165</v>
+      </c>
+      <c r="T21" t="n">
+        <v>140</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>biceps</t>
+          <t>overhead extension (lat)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EZ bend</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>ez bar</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>s-n/n-p</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>x0.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>upright</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>165</v>
+      </c>
+      <c r="T22" t="n">
+        <v>140</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>curl (sag)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>biceps</t>
+          <t>overhead extension (sag)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EZ bend</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>ez bar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>s-n/n-p</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>sag</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>x0.5/x1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>upright</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>165</v>
+      </c>
+      <c r="T23" t="n">
+        <v>140</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bayesian curl</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>biceps</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>d-handle fix</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>dumbell</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>sup</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>sup/s-n/n/n-p</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>sag</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1-8</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>incl</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="n">
+        <v>145</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>crossbody curl</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>concentration curl</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>biceps</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>d-handle fix</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
         <is>
           <t>sup</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>16-22</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>s-t</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>90/90os</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>sitting</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>40</v>
+      </c>
+      <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>145</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>face pull</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>spider curl</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nooses</t>
+          <t>biceps</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>n/n-p/pro</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1-8</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>incl</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>plane</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>90</v>
+      </c>
+      <c r="T26" t="n">
+        <v>10</v>
+      </c>
+      <c r="U26" t="n">
+        <v>145</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>face pull (t-l)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nooses</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>t-l</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>trans/t-l</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>flat/incl</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>25</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80</v>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>20</v>
+      </c>
       <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>skull crusher (s-t)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>triceps</t>
+          <t>press (sag/s-t/trans)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nose bar</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>s-n/n-p</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>s-t</t>
+          <t>n</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>x0.5/x1</t>
+          <t>sag/s-t/trans</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>flat/incl</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>incl</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>lying</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>85</v>
+      </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>90</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>skull crusher (sag)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>triceps</t>
+          <t>press (trans)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nose bar</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>s-n/n-p</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>sag</t>
+          <t>pro</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>x0.5/x1</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>flat/incl</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>lying</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>45</v>
+      </c>
+      <c r="R29" t="n">
+        <v>85</v>
+      </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>90</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>concentration curl</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>biceps</t>
+          <t>press</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>sup</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>s-t</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>lat/l-s</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>upright</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>sitting</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>90</v>
+      </c>
+      <c r="R30" t="n">
+        <v>160</v>
+      </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>90</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>spider curl</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>biceps</t>
+          <t>kelso shrugg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>sup</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+          <t>n-p</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>trans/t-l</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -2360,60 +2916,64 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>press (sag/s-t/trans)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>shrugg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>sag/s-t/trans</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>incl</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>plane</t>
+          <t>sitting</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -2421,353 +2981,451 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>press (trans)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>rear raise (t-l)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>pro</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>trans</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>t-l</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
+          <t>sitting</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>30</v>
+      </c>
+      <c r="R33" t="n">
+        <v>90</v>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>20</v>
+      </c>
       <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>press (lat)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>rear raise (trans/t-l)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>shoulder</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>barbell</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>pro</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>x1.5</t>
+          <t>trans/t-l</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>flat/incl</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="n">
+        <v>90</v>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>20</v>
+      </c>
       <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>press (lat/l-s)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>lateral raise</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>shoulder</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>lat/l-s</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>n/n-p</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>upright</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>sitting</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>80</v>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>10</v>
+      </c>
       <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kelso shrugg</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>Y raise</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>n-p</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>trans/t-l</t>
+          <t>sup/s-n/n/n-p</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>l-s</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>incl</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>lying</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>sitting</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>120</v>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>10</v>
+      </c>
       <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>shrugg</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>front raise</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>n/n-p/pro</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>s-n/n/n-p/pro</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>upright</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lying</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>body_pos</t>
+          <t>sitting</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>90</v>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>10</v>
+      </c>
       <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shrugg (sitting)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>flexion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>sag</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>sitting</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>body_pos</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2775,56 +3433,64 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rear raise (t-l)</t>
+          <t>Bench + Freeweight</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>dumbell</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>pro</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>t-l</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>sitting</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2832,43 +3498,51 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rear raise (trans/t-l)</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>pushdown</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dumbell</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>EZ bend</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>pro</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>trans/t-l</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>n-p</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>flat/incl</t>
+          <t>16-22</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -2876,162 +3550,228 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="n">
+        <v>110</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Y raise</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>extension (l-s)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dumbell</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>nooses</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>sup/s-n/n/n-p</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>l-s</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>incl</t>
+          <t>16-22</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>lying</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>sitting</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>flexion</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>forearm</t>
+          <t>extension (lat)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>d-handle var</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nooses</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>flexion (sag)</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>forearm</t>
+          <t>extension (sag)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dumbell</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>cuff</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>sag</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>16-22</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -3039,734 +3779,1034 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>sitting</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>forearm</t>
+          <t>overhead extension (l-s)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>d-handle var</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EZ bend</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>l-s</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>165</v>
+      </c>
+      <c r="T44" t="n">
+        <v>140</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>extension (sag)</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>forearm</t>
+          <t>overhead extension (lat)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dumbell</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1rope</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>sag</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>sitting</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>165</v>
+      </c>
+      <c r="T45" t="n">
+        <v>140</v>
+      </c>
+      <c r="U45" t="n">
+        <v>10</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rev fly</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>overhead extension (sag)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>1rope</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>trans</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>9-15/16-22</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>90/135</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>165</v>
+      </c>
+      <c r="T46" t="n">
+        <v>140</v>
+      </c>
+      <c r="U46" t="n">
+        <v>10</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kenan flap</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cuff</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>16-22</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>bench_cable</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="n">
+        <v>10</v>
+      </c>
+      <c r="U47" t="n">
+        <v>145</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pull</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>curl (0)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>d-handle var</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>sup/s-n/n/n-p/pro</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>16-22</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EZ bend</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>bench_cable</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="n">
+        <v>10</v>
+      </c>
+      <c r="U48" t="n">
+        <v>145</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pull (lat/sag)</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>fly (t-l/1-8)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>long light bend</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>lat/sag</t>
+          <t>sup</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>x1/x1.5</t>
+          <t>t-l</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>plane/cable_h</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>25</v>
+      </c>
+      <c r="R49" t="n">
+        <v>80</v>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>20</v>
+      </c>
       <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>crunch</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>fly (t-l/16-22)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ropes</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>sup/s-n</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>t-l</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>plane/cable_h</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>25</v>
+      </c>
+      <c r="R50" t="n">
+        <v>80</v>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>20</v>
+      </c>
       <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>fly (trans)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mag close n-s</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>s-n</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>sag</t>
+          <t>sup/s-n</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>x0.5</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9-15</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>25</v>
+      </c>
+      <c r="R51" t="n">
+        <v>80</v>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>20</v>
+      </c>
       <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rear pull</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>archer pull</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>shoulder</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>cuff</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>n/n-p/pro</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>9-15</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>90/135</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>60</v>
+      </c>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>120</v>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rear pull (trans)</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>rev fly</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>shoulder</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>nooses</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>sup/s-n/n/n-p</t>
-        </is>
-      </c>
+          <t>1rope</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>trans</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>x1.5</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9-15/16-22</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>plane</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>90/135</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>30</v>
+      </c>
+      <c r="R53" t="n">
+        <v>90</v>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>20</v>
+      </c>
       <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>front raise</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>long light bend</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>ropes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>pro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>sag</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1-8</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>90</v>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>10</v>
+      </c>
       <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>kenan flap</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>back</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>d-handle fix</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>sup/s-n/n/n-p/pro</t>
-        </is>
-      </c>
+          <t>cuff</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>sag/s-t/trans</t>
+          <t>n</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>30</v>
+      </c>
+      <c r="R55" t="n">
+        <v>90</v>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="n">
+        <v>90</v>
+      </c>
       <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>back row</t>
+          <t>cable + bench</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>pull</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>sup/pro</t>
-        </is>
-      </c>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>l-s/sag</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>x1</t>
-        </is>
-      </c>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>160</v>
+      </c>
+      <c r="R56" t="n">
+        <v>30</v>
+      </c>
       <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>10</v>
+      </c>
+      <c r="U56" t="n">
+        <v>90</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>deadlift</t>
+          <t>Lat pull</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>pull</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>long light bend</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>sup/pro</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>lat/sag</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>x1/x1.5</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3774,45 +4814,61 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>160</v>
+      </c>
+      <c r="R57" t="n">
+        <v>30</v>
+      </c>
       <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>10</v>
+      </c>
+      <c r="U57" t="n">
+        <v>90</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hyperextension</t>
+          <t>Lat pull</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>glute</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>plates</t>
+          <t>triceps</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>cuff</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>sag</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -3823,34 +4879,60 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="n">
+        <v>100</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
+      </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>Lat pull</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>crunch</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>barbell</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ropes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3860,7 +4942,11 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -3868,40 +4954,52 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Romanian Deadlift</t>
+          <t>Lat pull</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>biceps</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>straight</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>pro</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>sup</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3909,36 +5007,70 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="n">
+        <v>10</v>
+      </c>
+      <c r="U60" t="n">
+        <v>145</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>Lat pull2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>pull</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dumbell</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>long light bend</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>lat/sag</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>x1/x1.5</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3946,14 +5078,1942 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>160</v>
+      </c>
+      <c r="R61" t="n">
+        <v>30</v>
+      </c>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="T61" t="n">
+        <v>10</v>
+      </c>
+      <c r="U61" t="n">
+        <v>90</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lat pull2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>triceps</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>cuff</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="n">
+        <v>100</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lat pull2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>crunch</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ropes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Lat pull2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>straight</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="n">
+        <v>10</v>
+      </c>
+      <c r="U64" t="n">
+        <v>145</v>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mag close n-s</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>s-n</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>x0.5</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>30</v>
+      </c>
+      <c r="R65" t="n">
+        <v>80</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="n">
+        <v>10</v>
+      </c>
+      <c r="U65" t="n">
+        <v>90</v>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>face pull</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>nooses</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>t-l</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>90</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>90</v>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>rear pull</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>nooses</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>trans</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>x1.5</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>90</v>
+      </c>
+      <c r="R67" t="n">
+        <v>30</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>90</v>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>long light bend</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>straight</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="n">
+        <v>10</v>
+      </c>
+      <c r="U69" t="n">
+        <v>145</v>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>flexion</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>lat row</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>d-handle fix</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>sag/s-t/trans</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>30</v>
+      </c>
+      <c r="R72" t="n">
+        <v>80</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="n">
+        <v>10</v>
+      </c>
+      <c r="U72" t="n">
+        <v>90</v>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>face pull</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>nooses</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>t-l</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>90</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>90</v>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>rear pull</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>cuff</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>90</v>
+      </c>
+      <c r="R74" t="n">
+        <v>30</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>90</v>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>long light bend</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>straight</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="n">
+        <v>10</v>
+      </c>
+      <c r="U76" t="n">
+        <v>145</v>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>flexion</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>lat row 2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>d-handle var</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>back row</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>l-s/sag</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>30</v>
+      </c>
+      <c r="R79" t="n">
+        <v>80</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="n">
+        <v>10</v>
+      </c>
+      <c r="U79" t="n">
+        <v>90</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>deadlift</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>shrugg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>hyperextension</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>glute</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>plates</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>x1.5</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>90</v>
+      </c>
+      <c r="R83" t="n">
+        <v>160</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="n">
+        <v>90</v>
+      </c>
+      <c r="U83" t="n">
+        <v>10</v>
+      </c>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>biceps</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EZ bar</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>s-n/n-p</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>x0.5/x1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>elbow</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="n">
+        <v>10</v>
+      </c>
+      <c r="U84" t="n">
+        <v>145</v>
+      </c>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>flexion</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>forearm</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>sup/pro</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Romanian Deadlift</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>not_modeled</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>lateral raise</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>n/n-p</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>80</v>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="n">
+        <v>10</v>
+      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>free + freeweight</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>front raise</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>dumbell</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>sup/s-n/n/n-p/pro</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>sag</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>90</v>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="n">
+        <v>10</v>
+      </c>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8723C8E-93A6-4F93-BF61-3FFC593E5D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCCC1AB-8488-478B-A1DE-BC5E5227C5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="179">
   <si>
     <t>Kombi</t>
   </si>
@@ -533,6 +533,30 @@
   </si>
   <si>
     <t>rot_shoulder_fix</t>
+  </si>
+  <si>
+    <t>elv_angle_world_start</t>
+  </si>
+  <si>
+    <t>elv_angle_world_end</t>
+  </si>
+  <si>
+    <t>elv_angle_world_fix</t>
+  </si>
+  <si>
+    <t>shoulder elv</t>
+  </si>
+  <si>
+    <t>elbow flex</t>
+  </si>
+  <si>
+    <t>angle (plane)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">angle (world) </t>
+  </si>
+  <si>
+    <t>rot shoulder</t>
   </si>
 </sst>
 </file>
@@ -554,7 +578,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -570,6 +594,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCDCD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -616,6 +646,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -925,285 +959,300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AF92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="14" width="12" customWidth="1"/>
-    <col min="15" max="16" width="18" customWidth="1"/>
-    <col min="17" max="28" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="8.21875" customWidth="1"/>
+    <col min="29" max="31" width="8.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Q1" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AE2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I3" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K3" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P3" t="s">
         <v>31</v>
-      </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="3"/>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>10</v>
-      </c>
-      <c r="U2" s="3">
-        <v>145</v>
-      </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="3"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="3"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>39</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="3"/>
+      <c r="S3">
+        <v>-45</v>
+      </c>
+      <c r="T3" s="2">
+        <v>10</v>
+      </c>
+      <c r="U3" s="3">
+        <v>145</v>
+      </c>
       <c r="W3" s="2"/>
       <c r="X3" s="3"/>
+      <c r="Y3">
+        <v>0</v>
+      </c>
       <c r="Z3" s="2"/>
       <c r="AA3" s="3"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" t="s">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>120</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="3"/>
       <c r="T4" s="2"/>
       <c r="U4" s="3"/>
-      <c r="V4">
-        <v>10</v>
-      </c>
       <c r="W4" s="2"/>
       <c r="X4" s="3"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="3"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="3"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>60</v>
-      </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <v>120</v>
+        <v>90</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="3"/>
+      <c r="V5">
+        <v>10</v>
       </c>
       <c r="W5" s="2"/>
       <c r="X5" s="3"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="3"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AB5">
+        <v>45</v>
+      </c>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -1215,233 +1264,278 @@
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
       </c>
       <c r="P6" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>60</v>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="3"/>
+      <c r="S6">
+        <v>90</v>
       </c>
       <c r="T6" s="2">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="U6" s="3">
-        <v>120</v>
-      </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="W6" s="2">
+        <v>-45</v>
+      </c>
+      <c r="X6" s="3">
+        <v>90</v>
+      </c>
       <c r="Z6" s="2"/>
       <c r="AA6" s="3"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" t="s">
+        <v>58</v>
       </c>
       <c r="P7" t="s">
         <v>54</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2"/>
+      <c r="R7" s="3"/>
+      <c r="S7">
+        <v>90</v>
+      </c>
+      <c r="T7" s="2">
+        <v>135</v>
+      </c>
+      <c r="U7" s="3">
         <v>30</v>
       </c>
-      <c r="R7" s="3">
-        <v>80</v>
-      </c>
-      <c r="T7" s="2">
-        <v>10</v>
-      </c>
-      <c r="U7" s="3">
+      <c r="W7" s="2">
+        <v>-45</v>
+      </c>
+      <c r="X7" s="3">
         <v>90</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="3"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="3"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" t="s">
-        <v>48</v>
+        <v>61</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
       </c>
       <c r="P8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="3"/>
-      <c r="S8">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>30</v>
+      </c>
+      <c r="R8" s="3">
+        <v>80</v>
       </c>
       <c r="T8" s="2">
         <v>10</v>
       </c>
       <c r="U8" s="3">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="W8" s="2"/>
       <c r="X8" s="3"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="3"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="3"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
       </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
+        <v>48</v>
+      </c>
       <c r="P9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="3"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="3"/>
+      <c r="S9">
+        <v>40</v>
+      </c>
+      <c r="T9" s="2">
+        <v>10</v>
+      </c>
+      <c r="U9" s="3">
+        <v>145</v>
+      </c>
       <c r="W9" s="2"/>
       <c r="X9" s="3"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="3"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="3"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
+        <v>32</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="P10" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="3"/>
-      <c r="S10">
-        <v>10</v>
-      </c>
-      <c r="T10" s="2">
-        <v>10</v>
-      </c>
-      <c r="U10" s="3">
-        <v>145</v>
-      </c>
-      <c r="W10" s="2">
-        <v>45</v>
-      </c>
+      <c r="T10" s="2"/>
+      <c r="U10" s="3"/>
+      <c r="W10" s="2"/>
       <c r="X10" s="3"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="3"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="3"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" t="s">
+        <v>69</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="3"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="3"/>
+      <c r="S11">
+        <v>90</v>
+      </c>
+      <c r="T11" s="2">
+        <v>10</v>
+      </c>
+      <c r="U11" s="3">
+        <v>145</v>
+      </c>
       <c r="W11" s="2"/>
       <c r="X11" s="3"/>
+      <c r="Y11">
+        <v>90</v>
+      </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C12" t="s">
@@ -1465,59 +1559,47 @@
       <c r="U12" s="3"/>
       <c r="W12" s="2"/>
       <c r="X12" s="3"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="3"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="5"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="3"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="P13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
-      <c r="S13">
-        <v>10</v>
-      </c>
-      <c r="T13" s="2">
-        <v>10</v>
-      </c>
-      <c r="U13" s="3">
-        <v>145</v>
-      </c>
+      <c r="T13" s="2"/>
+      <c r="U13" s="3"/>
       <c r="W13" s="2"/>
       <c r="X13" s="3"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="3"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="3"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
@@ -1526,22 +1608,22 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" t="s">
-        <v>47</v>
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" t="s">
+        <v>78</v>
       </c>
       <c r="P14" t="s">
         <v>31</v>
@@ -1552,19 +1634,27 @@
         <v>10</v>
       </c>
       <c r="T14" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>145</v>
       </c>
       <c r="W14" s="2"/>
       <c r="X14" s="3"/>
+      <c r="Y14">
+        <v>0</v>
+      </c>
       <c r="Z14" s="2"/>
       <c r="AA14" s="3"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>75</v>
@@ -1573,22 +1663,22 @@
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
       </c>
-      <c r="I15" t="s">
-        <v>29</v>
+      <c r="J15" t="s">
+        <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="P15" t="s">
         <v>31</v>
@@ -1596,7 +1686,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
       <c r="S15">
-        <v>10</v>
+        <v>-45</v>
       </c>
       <c r="T15" s="2">
         <v>10</v>
@@ -1608,10 +1698,18 @@
       <c r="X15" s="3"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="3"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AB15">
+        <v>45</v>
+      </c>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
@@ -1620,19 +1718,22 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
       </c>
-      <c r="H16" t="s">
-        <v>38</v>
+      <c r="I16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" t="s">
+        <v>80</v>
       </c>
       <c r="P16" t="s">
         <v>31</v>
@@ -1643,19 +1744,27 @@
         <v>10</v>
       </c>
       <c r="T16" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U16" s="3">
         <v>145</v>
       </c>
       <c r="W16" s="2"/>
       <c r="X16" s="3"/>
+      <c r="Y16">
+        <v>0</v>
+      </c>
       <c r="Z16" s="2"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
         <v>75</v>
@@ -1684,22 +1793,30 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="3"/>
       <c r="S17">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="T17" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="U17" s="3">
         <v>145</v>
       </c>
       <c r="W17" s="2"/>
       <c r="X17" s="3"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="3"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="5"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
         <v>75</v>
@@ -1714,7 +1831,7 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1728,22 +1845,30 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="3"/>
       <c r="S18">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="T18" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="U18" s="3">
         <v>145</v>
       </c>
       <c r="W18" s="2"/>
       <c r="X18" s="3"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="3"/>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="5"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
@@ -1784,10 +1909,15 @@
       <c r="X19" s="3"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
         <v>75</v>
@@ -1796,19 +1926,19 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="P20" t="s">
         <v>31</v>
@@ -1828,19 +1958,24 @@
       <c r="X20" s="3"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="3"/>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="3"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
       </c>
       <c r="F21" t="s">
         <v>77</v>
@@ -1848,14 +1983,8 @@
       <c r="G21" t="s">
         <v>28</v>
       </c>
-      <c r="I21" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>80</v>
+      <c r="H21" t="s">
+        <v>85</v>
       </c>
       <c r="P21" t="s">
         <v>31</v>
@@ -1875,13 +2004,15 @@
       <c r="X21" s="3"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="3"/>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="3"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -1889,9 +2020,6 @@
       <c r="D22" t="s">
         <v>76</v>
       </c>
-      <c r="E22" t="s">
-        <v>36</v>
-      </c>
       <c r="F22" t="s">
         <v>77</v>
       </c>
@@ -1901,14 +2029,11 @@
       <c r="I22" t="s">
         <v>29</v>
       </c>
-      <c r="K22" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" t="s">
-        <v>79</v>
+      <c r="L22">
+        <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P22" t="s">
         <v>31</v>
@@ -1926,61 +2051,84 @@
       </c>
       <c r="W22" s="2"/>
       <c r="X22" s="3"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="3"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="5"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="3"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
         <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" t="s">
-        <v>38</v>
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" t="s">
+        <v>78</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="3"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="3"/>
+      <c r="S23">
+        <v>10</v>
+      </c>
+      <c r="T23" s="2">
+        <v>10</v>
+      </c>
+      <c r="U23" s="3">
+        <v>145</v>
+      </c>
       <c r="W23" s="2"/>
       <c r="X23" s="3"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="3"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="3"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
         <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="H24" t="s">
         <v>38</v>
@@ -1996,10 +2144,12 @@
       <c r="X24" s="3"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="3"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="3"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
         <v>89</v>
@@ -2030,31 +2180,30 @@
       <c r="X25" s="3"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="3"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="3"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" t="s">
-        <v>92</v>
-      </c>
-      <c r="N26" t="s">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="H26" t="s">
+        <v>38</v>
       </c>
       <c r="P26" t="s">
         <v>39</v>
@@ -2067,10 +2216,12 @@
       <c r="X26" s="3"/>
       <c r="Z26" s="2"/>
       <c r="AA26" s="3"/>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="3"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
         <v>89</v>
@@ -2079,10 +2230,19 @@
         <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
         <v>61</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" t="s">
+        <v>92</v>
+      </c>
+      <c r="N27" t="s">
+        <v>48</v>
       </c>
       <c r="P27" t="s">
         <v>39</v>
@@ -2093,12 +2253,14 @@
       <c r="U27" s="3"/>
       <c r="W27" s="2"/>
       <c r="X27" s="3"/>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="3"/>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="5"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="3"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
         <v>89</v>
@@ -2123,10 +2285,12 @@
       <c r="X28" s="3"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="3"/>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="3"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
@@ -2135,16 +2299,10 @@
         <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s">
         <v>61</v>
-      </c>
-      <c r="H29" t="s">
-        <v>38</v>
       </c>
       <c r="P29" t="s">
         <v>39</v>
@@ -2157,48 +2315,48 @@
       <c r="X29" s="3"/>
       <c r="Z29" s="2"/>
       <c r="AA29" s="3"/>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="3"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>35</v>
+      </c>
+      <c r="E30" t="s">
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" t="s">
-        <v>28</v>
+        <v>61</v>
+      </c>
+      <c r="H30" t="s">
+        <v>38</v>
       </c>
       <c r="P30" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" s="3"/>
-      <c r="S30">
-        <v>20</v>
-      </c>
-      <c r="T30" s="2">
-        <v>100</v>
-      </c>
-      <c r="U30" s="3">
-        <v>5</v>
-      </c>
+      <c r="T30" s="2"/>
+      <c r="U30" s="3"/>
       <c r="W30" s="2"/>
       <c r="X30" s="3"/>
       <c r="Z30" s="2"/>
       <c r="AA30" s="3"/>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="3"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
         <v>89</v>
@@ -2233,37 +2391,27 @@
       <c r="X31" s="3"/>
       <c r="Z31" s="2"/>
       <c r="AA31" s="3"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="3"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
         <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
         <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" t="s">
-        <v>68</v>
-      </c>
-      <c r="M32" t="s">
-        <v>79</v>
-      </c>
-      <c r="O32" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="P32" t="s">
         <v>31</v>
@@ -2281,15 +2429,17 @@
       </c>
       <c r="W32" s="2"/>
       <c r="X32" s="3"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="3"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="5"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="3"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>94</v>
@@ -2304,13 +2454,13 @@
         <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="I33" t="s">
         <v>68</v>
       </c>
-      <c r="K33" t="s">
-        <v>100</v>
+      <c r="M33" t="s">
+        <v>79</v>
       </c>
       <c r="O33" t="s">
         <v>78</v>
@@ -2333,10 +2483,12 @@
       <c r="X33" s="3"/>
       <c r="Z33" s="2"/>
       <c r="AA33" s="3"/>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="3"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
         <v>99</v>
@@ -2359,8 +2511,8 @@
       <c r="I34" t="s">
         <v>68</v>
       </c>
-      <c r="M34" t="s">
-        <v>79</v>
+      <c r="K34" t="s">
+        <v>100</v>
       </c>
       <c r="O34" t="s">
         <v>78</v>
@@ -2383,13 +2535,15 @@
       <c r="X34" s="3"/>
       <c r="Z34" s="2"/>
       <c r="AA34" s="3"/>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="3"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>94</v>
@@ -2404,12 +2558,12 @@
         <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I35" t="s">
         <v>68</v>
       </c>
-      <c r="K35" t="s">
+      <c r="M35" t="s">
         <v>79</v>
       </c>
       <c r="O35" t="s">
@@ -2433,10 +2587,12 @@
       <c r="X35" s="3"/>
       <c r="Z35" s="2"/>
       <c r="AA35" s="3"/>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="3"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
         <v>101</v>
@@ -2445,7 +2601,10 @@
         <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
       </c>
       <c r="F36" t="s">
         <v>96</v>
@@ -2456,7 +2615,7 @@
       <c r="I36" t="s">
         <v>68</v>
       </c>
-      <c r="M36" t="s">
+      <c r="K36" t="s">
         <v>79</v>
       </c>
       <c r="O36" t="s">
@@ -2480,58 +2639,61 @@
       <c r="X36" s="3"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="3"/>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="3"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>96</v>
+      </c>
+      <c r="G37" t="s">
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" t="s">
         <v>79</v>
       </c>
-      <c r="N37" t="s">
-        <v>79</v>
+      <c r="O37" t="s">
+        <v>78</v>
       </c>
       <c r="P37" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>0</v>
-      </c>
-      <c r="R37" s="3">
-        <v>90</v>
+        <v>31</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="3"/>
+      <c r="S37">
+        <v>20</v>
       </c>
       <c r="T37" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U37" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="W37" s="2"/>
       <c r="X37" s="3"/>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="3"/>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="5"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="3"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
         <v>102</v>
@@ -2546,10 +2708,16 @@
         <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G38" t="s">
-        <v>103</v>
+        <v>56</v>
+      </c>
+      <c r="I38" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" t="s">
+        <v>79</v>
+      </c>
+      <c r="N38" t="s">
+        <v>79</v>
       </c>
       <c r="P38" t="s">
         <v>54</v>
@@ -2570,10 +2738,12 @@
       <c r="X38" s="3"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="3"/>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="3"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
         <v>102</v>
@@ -2612,47 +2782,56 @@
       <c r="X39" s="3"/>
       <c r="Z39" s="2"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>98</v>
+      </c>
+      <c r="E40" t="s">
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
-      </c>
-      <c r="J40" t="s">
-        <v>92</v>
-      </c>
-      <c r="N40" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="P40" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="3"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>90</v>
+      </c>
+      <c r="T40" s="2">
+        <v>0</v>
+      </c>
+      <c r="U40" s="3">
+        <v>90</v>
+      </c>
       <c r="W40" s="2"/>
       <c r="X40" s="3"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>104</v>
@@ -2661,10 +2840,19 @@
         <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="F41" t="s">
         <v>61</v>
+      </c>
+      <c r="G41" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" t="s">
+        <v>92</v>
+      </c>
+      <c r="N41" t="s">
+        <v>48</v>
       </c>
       <c r="P41" t="s">
         <v>39</v>
@@ -2677,10 +2865,12 @@
       <c r="X41" s="3"/>
       <c r="Z41" s="2"/>
       <c r="AA41" s="3"/>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="3"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s">
         <v>104</v>
@@ -2703,12 +2893,14 @@
       <c r="U42" s="3"/>
       <c r="W42" s="2"/>
       <c r="X42" s="3"/>
-      <c r="Z42" s="2"/>
-      <c r="AA42" s="3"/>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="5"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="3"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
         <v>104</v>
@@ -2717,16 +2909,10 @@
         <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s">
         <v>61</v>
-      </c>
-      <c r="H43" t="s">
-        <v>38</v>
       </c>
       <c r="P43" t="s">
         <v>39</v>
@@ -2739,57 +2925,48 @@
       <c r="X43" s="3"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="3"/>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="3"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="E44" t="s">
         <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
-      </c>
-      <c r="G44" t="s">
-        <v>107</v>
-      </c>
-      <c r="I44" t="s">
-        <v>108</v>
-      </c>
-      <c r="K44" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="H44" t="s">
+        <v>38</v>
       </c>
       <c r="P44" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>25</v>
-      </c>
-      <c r="R44" s="3">
-        <v>80</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="3"/>
       <c r="T44" s="2"/>
       <c r="U44" s="3"/>
-      <c r="V44">
-        <v>20</v>
-      </c>
       <c r="W44" s="2"/>
       <c r="X44" s="3"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="3"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="3"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
         <v>105</v>
@@ -2798,22 +2975,22 @@
         <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="E45" t="s">
         <v>36</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>109</v>
-      </c>
-      <c r="J45" t="s">
-        <v>110</v>
-      </c>
-      <c r="M45" t="s">
-        <v>47</v>
+        <v>107</v>
+      </c>
+      <c r="I45" t="s">
+        <v>108</v>
+      </c>
+      <c r="K45" t="s">
+        <v>69</v>
       </c>
       <c r="P45" t="s">
         <v>42</v>
@@ -2833,37 +3010,36 @@
       <c r="X45" s="3"/>
       <c r="Z45" s="2"/>
       <c r="AA45" s="3"/>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="3"/>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E46" t="s">
         <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>103</v>
-      </c>
-      <c r="I46" t="s">
-        <v>29</v>
+        <v>109</v>
+      </c>
+      <c r="J46" t="s">
+        <v>110</v>
       </c>
       <c r="M46" t="s">
-        <v>112</v>
-      </c>
-      <c r="O46" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="P46" t="s">
         <v>42</v>
@@ -2883,13 +3059,15 @@
       <c r="X46" s="3"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="3"/>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="3"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>106</v>
@@ -2901,13 +3079,13 @@
         <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
         <v>103</v>
       </c>
       <c r="I47" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M47" t="s">
         <v>112</v>
@@ -2931,15 +3109,17 @@
       </c>
       <c r="W47" s="2"/>
       <c r="X47" s="3"/>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="3"/>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="5"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="3"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
         <v>106</v>
@@ -2954,16 +3134,16 @@
         <v>115</v>
       </c>
       <c r="G48" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="I48" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="M48" t="s">
         <v>112</v>
       </c>
       <c r="O48" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="P48" t="s">
         <v>42</v>
@@ -2983,57 +3163,64 @@
       <c r="X48" s="3"/>
       <c r="Z48" s="2"/>
       <c r="AA48" s="3"/>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="3"/>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I49" t="s">
-        <v>29</v>
-      </c>
-      <c r="K49" t="s">
-        <v>119</v>
+        <v>57</v>
+      </c>
+      <c r="M49" t="s">
+        <v>112</v>
+      </c>
+      <c r="O49" t="s">
+        <v>78</v>
       </c>
       <c r="P49" t="s">
         <v>42</v>
       </c>
       <c r="Q49" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R49" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="T49" s="2"/>
       <c r="U49" s="3"/>
       <c r="V49">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W49" s="2"/>
       <c r="X49" s="3"/>
       <c r="Z49" s="2"/>
       <c r="AA49" s="3"/>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="3"/>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
         <v>117</v>
@@ -3042,28 +3229,22 @@
         <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
         <v>118</v>
       </c>
       <c r="F50" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
         <v>28</v>
       </c>
-      <c r="H50" t="s">
-        <v>38</v>
-      </c>
-      <c r="J50" t="s">
-        <v>121</v>
-      </c>
-      <c r="M50" t="s">
-        <v>47</v>
-      </c>
-      <c r="N50" t="s">
-        <v>48</v>
+      <c r="I50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" t="s">
+        <v>119</v>
       </c>
       <c r="P50" t="s">
         <v>42</v>
@@ -3083,10 +3264,12 @@
       <c r="X50" s="3"/>
       <c r="Z50" s="2"/>
       <c r="AA50" s="3"/>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="3"/>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
         <v>117</v>
@@ -3095,22 +3278,28 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>118</v>
+      </c>
+      <c r="F51" t="s">
+        <v>120</v>
       </c>
       <c r="G51" t="s">
         <v>28</v>
       </c>
-      <c r="I51" t="s">
-        <v>29</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
+      <c r="H51" t="s">
+        <v>38</v>
+      </c>
+      <c r="J51" t="s">
+        <v>121</v>
       </c>
       <c r="M51" t="s">
-        <v>79</v>
+        <v>47</v>
+      </c>
+      <c r="N51" t="s">
+        <v>48</v>
       </c>
       <c r="P51" t="s">
         <v>42</v>
@@ -3130,10 +3319,12 @@
       <c r="X51" s="3"/>
       <c r="Z51" s="2"/>
       <c r="AA51" s="3"/>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="3"/>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>117</v>
@@ -3142,19 +3333,22 @@
         <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
-      </c>
-      <c r="F52" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="G52" t="s">
         <v>28</v>
       </c>
-      <c r="H52" t="s">
-        <v>38</v>
+      <c r="I52" t="s">
+        <v>29</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
+        <v>79</v>
       </c>
       <c r="P52" t="s">
         <v>42</v>
@@ -3172,121 +3366,128 @@
       </c>
       <c r="W52" s="2"/>
       <c r="X52" s="3"/>
-      <c r="Z52" s="2"/>
-      <c r="AA52" s="3"/>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="5"/>
+      <c r="AC52" s="2"/>
+      <c r="AD52" s="3"/>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
         <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G53" t="s">
-        <v>67</v>
-      </c>
-      <c r="I53" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" t="s">
-        <v>119</v>
+        <v>28</v>
+      </c>
+      <c r="H53" t="s">
+        <v>38</v>
       </c>
       <c r="P53" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="Q53" s="2">
         <v>0</v>
       </c>
       <c r="R53" s="3">
-        <v>80</v>
-      </c>
-      <c r="T53" s="2">
-        <v>0</v>
-      </c>
-      <c r="U53" s="3">
         <v>90</v>
+      </c>
+      <c r="T53" s="2"/>
+      <c r="U53" s="3"/>
+      <c r="V53">
+        <v>10</v>
       </c>
       <c r="W53" s="2"/>
       <c r="X53" s="3"/>
       <c r="Z53" s="2"/>
       <c r="AA53" s="3"/>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="3"/>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
         <v>36</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
-      </c>
-      <c r="H54" t="s">
-        <v>38</v>
+        <v>56</v>
+      </c>
+      <c r="G54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" t="s">
+        <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="3"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>80</v>
+      </c>
+      <c r="T54" s="2">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3">
+        <v>90</v>
+      </c>
       <c r="W54" s="2"/>
       <c r="X54" s="3"/>
       <c r="Z54" s="2"/>
       <c r="AA54" s="3"/>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="3"/>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="E55" t="s">
         <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>127</v>
-      </c>
-      <c r="G55" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="H55" t="s">
         <v>38</v>
-      </c>
-      <c r="J55" t="s">
-        <v>46</v>
-      </c>
-      <c r="N55" t="s">
-        <v>30</v>
       </c>
       <c r="P55" t="s">
         <v>39</v>
@@ -3299,98 +3500,103 @@
       <c r="X55" s="3"/>
       <c r="Z55" s="2"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC55" s="2"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
         <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>95</v>
+        <v>43</v>
+      </c>
+      <c r="E56" t="s">
+        <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="G56" t="s">
-        <v>67</v>
-      </c>
-      <c r="I56" t="s">
-        <v>68</v>
-      </c>
-      <c r="M56" t="s">
-        <v>53</v>
+        <v>109</v>
+      </c>
+      <c r="H56" t="s">
+        <v>38</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+      <c r="N56" t="s">
+        <v>30</v>
       </c>
       <c r="P56" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>30</v>
-      </c>
-      <c r="R56" s="3">
-        <v>90</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="3"/>
       <c r="T56" s="2"/>
       <c r="U56" s="3"/>
-      <c r="V56">
-        <v>90</v>
-      </c>
       <c r="W56" s="2"/>
       <c r="X56" s="3"/>
       <c r="Z56" s="2"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC56" s="2"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D57" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F57" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="G57" t="s">
         <v>67</v>
       </c>
       <c r="I57" t="s">
-        <v>131</v>
-      </c>
-      <c r="K57" t="s">
+        <v>68</v>
+      </c>
+      <c r="M57" t="s">
         <v>53</v>
       </c>
       <c r="P57" t="s">
         <v>42</v>
       </c>
       <c r="Q57" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R57" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T57" s="2"/>
       <c r="U57" s="3"/>
       <c r="V57">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="W57" s="2"/>
       <c r="X57" s="3"/>
-      <c r="Z57" s="2"/>
-      <c r="AA57" s="3"/>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="5"/>
+      <c r="AC57" s="2"/>
+      <c r="AD57" s="3"/>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
         <v>129</v>
@@ -3399,10 +3605,7 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F58" t="s">
         <v>130</v>
@@ -3410,8 +3613,11 @@
       <c r="G58" t="s">
         <v>67</v>
       </c>
-      <c r="N58" t="s">
-        <v>48</v>
+      <c r="I58" t="s">
+        <v>131</v>
+      </c>
+      <c r="K58" t="s">
+        <v>53</v>
       </c>
       <c r="P58" t="s">
         <v>42</v>
@@ -3431,10 +3637,12 @@
       <c r="X58" s="3"/>
       <c r="Z58" s="2"/>
       <c r="AA58" s="3"/>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC58" s="2"/>
+      <c r="AD58" s="3"/>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
         <v>129</v>
@@ -3453,6 +3661,9 @@
       </c>
       <c r="G59" t="s">
         <v>67</v>
+      </c>
+      <c r="N59" t="s">
+        <v>48</v>
       </c>
       <c r="P59" t="s">
         <v>42</v>
@@ -3472,81 +3683,76 @@
       <c r="X59" s="3"/>
       <c r="Z59" s="2"/>
       <c r="AA59" s="3"/>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC59" s="2"/>
+      <c r="AD59" s="3"/>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="D60" t="s">
         <v>43</v>
       </c>
+      <c r="E60" t="s">
+        <v>36</v>
+      </c>
       <c r="F60" t="s">
-        <v>127</v>
-      </c>
-      <c r="H60" t="s">
-        <v>133</v>
-      </c>
-      <c r="J60" t="s">
-        <v>121</v>
-      </c>
-      <c r="M60" t="s">
-        <v>47</v>
-      </c>
-      <c r="O60" t="s">
-        <v>78</v>
+        <v>130</v>
+      </c>
+      <c r="G60" t="s">
+        <v>67</v>
       </c>
       <c r="P60" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="3"/>
-      <c r="S60">
-        <v>165</v>
-      </c>
-      <c r="T60" s="2">
-        <v>140</v>
-      </c>
-      <c r="U60" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>80</v>
+      </c>
+      <c r="T60" s="2"/>
+      <c r="U60" s="3"/>
+      <c r="V60">
         <v>10</v>
       </c>
       <c r="W60" s="2"/>
       <c r="X60" s="3"/>
       <c r="Z60" s="2"/>
       <c r="AA60" s="3"/>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC60" s="2"/>
+      <c r="AD60" s="3"/>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C61" t="s">
         <v>94</v>
       </c>
       <c r="D61" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" t="s">
-        <v>45</v>
-      </c>
-      <c r="I61" t="s">
-        <v>57</v>
-      </c>
-      <c r="K61" t="s">
-        <v>30</v>
+        <v>127</v>
+      </c>
+      <c r="H61" t="s">
+        <v>133</v>
+      </c>
+      <c r="J61" t="s">
+        <v>121</v>
+      </c>
+      <c r="M61" t="s">
+        <v>47</v>
       </c>
       <c r="O61" t="s">
         <v>78</v>
@@ -3569,10 +3775,12 @@
       <c r="X61" s="3"/>
       <c r="Z61" s="2"/>
       <c r="AA61" s="3"/>
-    </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC61" s="2"/>
+      <c r="AD61" s="3"/>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
         <v>134</v>
@@ -3581,25 +3789,22 @@
         <v>94</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
       </c>
       <c r="F62" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G62" t="s">
         <v>45</v>
       </c>
-      <c r="H62" t="s">
-        <v>85</v>
-      </c>
-      <c r="J62" t="s">
-        <v>121</v>
-      </c>
-      <c r="M62" t="s">
-        <v>47</v>
+      <c r="I62" t="s">
+        <v>57</v>
+      </c>
+      <c r="K62" t="s">
+        <v>30</v>
       </c>
       <c r="O62" t="s">
         <v>78</v>
@@ -3620,12 +3825,14 @@
       </c>
       <c r="W62" s="2"/>
       <c r="X62" s="3"/>
-      <c r="Z62" s="2"/>
-      <c r="AA62" s="3"/>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="5"/>
+      <c r="AC62" s="2"/>
+      <c r="AD62" s="3"/>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
         <v>134</v>
@@ -3634,7 +3841,7 @@
         <v>94</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
         <v>36</v>
@@ -3645,8 +3852,14 @@
       <c r="G63" t="s">
         <v>45</v>
       </c>
+      <c r="H63" t="s">
+        <v>85</v>
+      </c>
+      <c r="J63" t="s">
+        <v>121</v>
+      </c>
       <c r="M63" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="O63" t="s">
         <v>78</v>
@@ -3669,34 +3882,33 @@
       <c r="X63" s="3"/>
       <c r="Z63" s="2"/>
       <c r="AA63" s="3"/>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC63" s="2"/>
+      <c r="AD63" s="3"/>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
         <v>94</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E64" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s">
-        <v>67</v>
-      </c>
-      <c r="I64" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" t="s">
-        <v>138</v>
+        <v>45</v>
+      </c>
+      <c r="M64" t="s">
+        <v>79</v>
       </c>
       <c r="O64" t="s">
         <v>78</v>
@@ -3719,10 +3931,12 @@
       <c r="X64" s="3"/>
       <c r="Z64" s="2"/>
       <c r="AA64" s="3"/>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC64" s="2"/>
+      <c r="AD64" s="3"/>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
         <v>136</v>
@@ -3731,25 +3945,22 @@
         <v>94</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F65" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
         <v>67</v>
       </c>
-      <c r="H65" t="s">
-        <v>133</v>
-      </c>
-      <c r="J65" t="s">
-        <v>121</v>
-      </c>
-      <c r="M65" t="s">
-        <v>47</v>
+      <c r="I65" t="s">
+        <v>57</v>
+      </c>
+      <c r="K65" t="s">
+        <v>138</v>
       </c>
       <c r="O65" t="s">
         <v>78</v>
@@ -3772,10 +3983,12 @@
       <c r="X65" s="3"/>
       <c r="Z65" s="2"/>
       <c r="AA65" s="3"/>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC65" s="2"/>
+      <c r="AD65" s="3"/>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B66" t="s">
         <v>136</v>
@@ -3784,16 +3997,25 @@
         <v>94</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="E66" t="s">
+        <v>36</v>
       </c>
       <c r="F66" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="G66" t="s">
         <v>67</v>
       </c>
+      <c r="H66" t="s">
+        <v>133</v>
+      </c>
+      <c r="J66" t="s">
+        <v>121</v>
+      </c>
       <c r="M66" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="O66" t="s">
         <v>78</v>
@@ -3816,34 +4038,30 @@
       <c r="X66" s="3"/>
       <c r="Z66" s="2"/>
       <c r="AA66" s="3"/>
-    </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC66" s="2"/>
+      <c r="AD66" s="3"/>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
         <v>94</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
-      </c>
-      <c r="E67" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="F67" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G67" t="s">
-        <v>28</v>
-      </c>
-      <c r="I67" t="s">
-        <v>57</v>
-      </c>
-      <c r="K67" t="s">
-        <v>138</v>
+        <v>67</v>
+      </c>
+      <c r="M67" t="s">
+        <v>100</v>
       </c>
       <c r="O67" t="s">
         <v>78</v>
@@ -3864,12 +4082,14 @@
       </c>
       <c r="W67" s="2"/>
       <c r="X67" s="3"/>
-      <c r="Z67" s="2"/>
-      <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="5"/>
+      <c r="AC67" s="2"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
         <v>140</v>
@@ -3878,25 +4098,22 @@
         <v>94</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F68" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G68" t="s">
         <v>28</v>
       </c>
-      <c r="H68" t="s">
-        <v>85</v>
-      </c>
-      <c r="J68" t="s">
-        <v>121</v>
-      </c>
-      <c r="M68" t="s">
-        <v>47</v>
+      <c r="I68" t="s">
+        <v>57</v>
+      </c>
+      <c r="K68" t="s">
+        <v>138</v>
       </c>
       <c r="O68" t="s">
         <v>78</v>
@@ -3919,10 +4136,12 @@
       <c r="X68" s="3"/>
       <c r="Z68" s="2"/>
       <c r="AA68" s="3"/>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC68" s="2"/>
+      <c r="AD68" s="3"/>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
         <v>140</v>
@@ -3931,16 +4150,25 @@
         <v>94</v>
       </c>
       <c r="D69" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="E69" t="s">
+        <v>36</v>
       </c>
       <c r="F69" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s">
         <v>28</v>
       </c>
+      <c r="H69" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" t="s">
+        <v>121</v>
+      </c>
       <c r="M69" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="O69" t="s">
         <v>78</v>
@@ -3963,49 +4191,44 @@
       <c r="X69" s="3"/>
       <c r="Z69" s="2"/>
       <c r="AA69" s="3"/>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC69" s="2"/>
+      <c r="AD69" s="3"/>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
-      </c>
-      <c r="E70" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="F70" t="s">
         <v>51</v>
       </c>
       <c r="G70" t="s">
-        <v>142</v>
-      </c>
-      <c r="J70" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="M70" t="s">
-        <v>47</v>
-      </c>
-      <c r="N70" t="s">
-        <v>48</v>
+        <v>79</v>
+      </c>
+      <c r="O70" t="s">
+        <v>78</v>
       </c>
       <c r="P70" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q70" s="2">
-        <v>90</v>
-      </c>
-      <c r="R70" s="3">
-        <v>160</v>
+        <v>31</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="3"/>
+      <c r="S70">
+        <v>165</v>
       </c>
       <c r="T70" s="2">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="U70" s="3">
         <v>10</v>
@@ -4014,10 +4237,12 @@
       <c r="X70" s="3"/>
       <c r="Z70" s="2"/>
       <c r="AA70" s="3"/>
-    </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC70" s="2"/>
+      <c r="AD70" s="3"/>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B71" t="s">
         <v>141</v>
@@ -4026,7 +4251,7 @@
         <v>42</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E71" t="s">
         <v>36</v>
@@ -4035,10 +4260,16 @@
         <v>51</v>
       </c>
       <c r="G71" t="s">
-        <v>67</v>
-      </c>
-      <c r="H71" t="s">
-        <v>143</v>
+        <v>142</v>
+      </c>
+      <c r="J71" t="s">
+        <v>121</v>
+      </c>
+      <c r="M71" t="s">
+        <v>47</v>
+      </c>
+      <c r="N71" t="s">
+        <v>48</v>
       </c>
       <c r="P71" t="s">
         <v>54</v>
@@ -4059,19 +4290,21 @@
       <c r="X71" s="3"/>
       <c r="Z71" s="2"/>
       <c r="AA71" s="3"/>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC71" s="2"/>
+      <c r="AD71" s="3"/>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E72" t="s">
         <v>36</v>
@@ -4080,61 +4313,57 @@
         <v>51</v>
       </c>
       <c r="G72" t="s">
-        <v>145</v>
-      </c>
-      <c r="J72" t="s">
-        <v>46</v>
-      </c>
-      <c r="M72" t="s">
-        <v>47</v>
-      </c>
-      <c r="O72" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="H72" t="s">
+        <v>143</v>
       </c>
       <c r="P72" t="s">
         <v>54</v>
       </c>
       <c r="Q72" s="2">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R72" s="3">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="T72" s="2">
         <v>90</v>
       </c>
       <c r="U72" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W72" s="2"/>
       <c r="X72" s="3"/>
-      <c r="Z72" s="2"/>
-      <c r="AA72" s="3"/>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="5"/>
+      <c r="AC72" s="2"/>
+      <c r="AD72" s="3"/>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C73" t="s">
         <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E73" t="s">
         <v>36</v>
       </c>
       <c r="F73" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G73" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="M73" t="s">
         <v>47</v>
@@ -4161,49 +4390,65 @@
       <c r="X73" s="3"/>
       <c r="Z73" s="2"/>
       <c r="AA73" s="3"/>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC73" s="2"/>
+      <c r="AD73" s="3"/>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>93</v>
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>96</v>
-      </c>
-      <c r="I74" t="s">
-        <v>68</v>
+        <v>37</v>
+      </c>
+      <c r="G74" t="s">
+        <v>52</v>
+      </c>
+      <c r="J74" t="s">
+        <v>92</v>
+      </c>
+      <c r="M74" t="s">
+        <v>47</v>
+      </c>
+      <c r="O74" t="s">
+        <v>78</v>
       </c>
       <c r="P74" t="s">
         <v>54</v>
       </c>
       <c r="Q74" s="2">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="R74" s="3">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="T74" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="U74" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="W74" s="2"/>
       <c r="X74" s="3"/>
       <c r="Z74" s="2"/>
       <c r="AA74" s="3"/>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC74" s="2"/>
+      <c r="AD74" s="3"/>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
         <v>147</v>
@@ -4212,19 +4457,13 @@
         <v>67</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
-      </c>
-      <c r="E75" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
-      </c>
-      <c r="G75" t="s">
-        <v>148</v>
-      </c>
-      <c r="H75" t="s">
-        <v>149</v>
+        <v>96</v>
+      </c>
+      <c r="I75" t="s">
+        <v>68</v>
       </c>
       <c r="P75" t="s">
         <v>54</v>
@@ -4245,10 +4484,12 @@
       <c r="X75" s="3"/>
       <c r="Z75" s="2"/>
       <c r="AA75" s="3"/>
-    </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC75" s="2"/>
+      <c r="AD75" s="3"/>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B76" t="s">
         <v>147</v>
@@ -4290,57 +4531,59 @@
       <c r="X76" s="3"/>
       <c r="Z76" s="2"/>
       <c r="AA76" s="3"/>
-    </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC76" s="2"/>
+      <c r="AD76" s="3"/>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E77" t="s">
         <v>36</v>
       </c>
       <c r="F77" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G77" t="s">
-        <v>45</v>
-      </c>
-      <c r="I77" t="s">
-        <v>68</v>
-      </c>
-      <c r="K77" t="s">
-        <v>79</v>
+        <v>148</v>
+      </c>
+      <c r="H77" t="s">
+        <v>149</v>
       </c>
       <c r="P77" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="3"/>
-      <c r="S77">
-        <v>15</v>
+        <v>54</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>160</v>
+      </c>
+      <c r="R77" s="3">
+        <v>30</v>
       </c>
       <c r="T77" s="2">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="U77" s="3">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="W77" s="2"/>
       <c r="X77" s="3"/>
-      <c r="Z77" s="2"/>
-      <c r="AA77" s="3"/>
-    </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="5"/>
+      <c r="AC77" s="2"/>
+      <c r="AD77" s="3"/>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B78" t="s">
         <v>150</v>
@@ -4358,12 +4601,12 @@
         <v>127</v>
       </c>
       <c r="G78" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="I78" t="s">
         <v>68</v>
       </c>
-      <c r="M78" t="s">
+      <c r="K78" t="s">
         <v>79</v>
       </c>
       <c r="P78" t="s">
@@ -4384,55 +4627,61 @@
       <c r="X78" s="3"/>
       <c r="Z78" s="2"/>
       <c r="AA78" s="3"/>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC78" s="2"/>
+      <c r="AD78" s="3"/>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E79" t="s">
         <v>36</v>
       </c>
       <c r="F79" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="G79" t="s">
-        <v>52</v>
-      </c>
-      <c r="H79" t="s">
-        <v>143</v>
+        <v>67</v>
+      </c>
+      <c r="I79" t="s">
+        <v>68</v>
+      </c>
+      <c r="M79" t="s">
+        <v>79</v>
       </c>
       <c r="P79" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q79" s="2">
-        <v>90</v>
-      </c>
-      <c r="R79" s="3">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="3"/>
+      <c r="S79">
+        <v>15</v>
       </c>
       <c r="T79" s="2">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="U79" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="W79" s="2"/>
       <c r="X79" s="3"/>
       <c r="Z79" s="2"/>
       <c r="AA79" s="3"/>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC79" s="2"/>
+      <c r="AD79" s="3"/>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="s">
         <v>151</v>
@@ -4441,16 +4690,19 @@
         <v>42</v>
       </c>
       <c r="D80" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E80" t="s">
         <v>36</v>
       </c>
       <c r="F80" t="s">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="G80" t="s">
+        <v>52</v>
       </c>
       <c r="H80" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="P80" t="s">
         <v>54</v>
@@ -4471,60 +4723,59 @@
       <c r="X80" s="3"/>
       <c r="Z80" s="2"/>
       <c r="AA80" s="3"/>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC80" s="2"/>
+      <c r="AD80" s="3"/>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C81" t="s">
         <v>42</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E81" t="s">
         <v>36</v>
       </c>
       <c r="F81" t="s">
-        <v>37</v>
-      </c>
-      <c r="G81" t="s">
-        <v>103</v>
-      </c>
-      <c r="N81" t="s">
-        <v>48</v>
-      </c>
-      <c r="O81" t="s">
-        <v>78</v>
+        <v>56</v>
+      </c>
+      <c r="H81" t="s">
+        <v>38</v>
       </c>
       <c r="P81" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Q81" s="2">
+        <v>90</v>
+      </c>
+      <c r="R81" s="3">
         <v>30</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="2">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>90</v>
-      </c>
-      <c r="T81" s="2"/>
-      <c r="U81" s="3"/>
-      <c r="V81">
-        <v>20</v>
       </c>
       <c r="W81" s="2"/>
       <c r="X81" s="3"/>
       <c r="Z81" s="2"/>
       <c r="AA81" s="3"/>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC81" s="2"/>
+      <c r="AD81" s="3"/>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
         <v>42</v>
@@ -4539,13 +4790,10 @@
         <v>37</v>
       </c>
       <c r="G82" t="s">
-        <v>109</v>
-      </c>
-      <c r="J82" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="N82" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="O82" t="s">
         <v>78</v>
@@ -4566,33 +4814,41 @@
       </c>
       <c r="W82" s="2"/>
       <c r="X82" s="3"/>
-      <c r="Z82" s="2"/>
-      <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="5"/>
+      <c r="AC82" s="2"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>42</v>
       </c>
       <c r="D83" t="s">
-        <v>139</v>
+        <v>43</v>
+      </c>
+      <c r="E83" t="s">
+        <v>36</v>
       </c>
       <c r="F83" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G83" t="s">
-        <v>52</v>
-      </c>
-      <c r="I83" t="s">
-        <v>155</v>
-      </c>
-      <c r="M83" t="s">
-        <v>58</v>
+        <v>109</v>
+      </c>
+      <c r="J83" t="s">
+        <v>110</v>
+      </c>
+      <c r="N83" t="s">
+        <v>30</v>
+      </c>
+      <c r="O83" t="s">
+        <v>78</v>
       </c>
       <c r="P83" t="s">
         <v>42</v>
@@ -4612,76 +4868,79 @@
       <c r="X83" s="3"/>
       <c r="Z83" s="2"/>
       <c r="AA83" s="3"/>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC83" s="2"/>
+      <c r="AD83" s="3"/>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="F84" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G84" t="s">
-        <v>145</v>
-      </c>
-      <c r="H84" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="I84" t="s">
+        <v>155</v>
+      </c>
+      <c r="M84" t="s">
+        <v>58</v>
       </c>
       <c r="P84" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="Q84" s="2">
         <v>30</v>
       </c>
       <c r="R84" s="3">
-        <v>80</v>
-      </c>
-      <c r="T84" s="2">
-        <v>10</v>
-      </c>
-      <c r="U84" s="3">
         <v>90</v>
+      </c>
+      <c r="T84" s="2"/>
+      <c r="U84" s="3"/>
+      <c r="V84">
+        <v>20</v>
       </c>
       <c r="W84" s="2"/>
       <c r="X84" s="3"/>
       <c r="Z84" s="2"/>
       <c r="AA84" s="3"/>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC84" s="2"/>
+      <c r="AD84" s="3"/>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
         <v>156</v>
       </c>
       <c r="C85" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
         <v>36</v>
       </c>
       <c r="F85" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="H85" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="P85" t="s">
         <v>54</v>
@@ -4702,47 +4961,59 @@
       <c r="X85" s="3"/>
       <c r="Z85" s="2"/>
       <c r="AA85" s="3"/>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC85" s="2"/>
+      <c r="AD85" s="3"/>
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C86" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D86" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="E86" t="s">
         <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>51</v>
+        <v>158</v>
+      </c>
+      <c r="G86" t="s">
+        <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>38</v>
-      </c>
-      <c r="N86" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="P86" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="3"/>
-      <c r="T86" s="2"/>
-      <c r="U86" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>30</v>
+      </c>
+      <c r="R86" s="3">
+        <v>80</v>
+      </c>
+      <c r="T86" s="2">
+        <v>10</v>
+      </c>
+      <c r="U86" s="3">
+        <v>90</v>
+      </c>
       <c r="W86" s="2"/>
       <c r="X86" s="3"/>
       <c r="Z86" s="2"/>
       <c r="AA86" s="3"/>
-    </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC86" s="2"/>
+      <c r="AD86" s="3"/>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -4757,10 +5028,13 @@
         <v>36</v>
       </c>
       <c r="F87" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H87" t="s">
         <v>38</v>
+      </c>
+      <c r="N87" t="s">
+        <v>48</v>
       </c>
       <c r="P87" t="s">
         <v>39</v>
@@ -4771,68 +5045,53 @@
       <c r="U87" s="3"/>
       <c r="W87" s="2"/>
       <c r="X87" s="3"/>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="3"/>
-    </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="5"/>
+      <c r="AC87" s="2"/>
+      <c r="AD87" s="3"/>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D88" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="E88" t="s">
         <v>36</v>
       </c>
       <c r="F88" t="s">
-        <v>77</v>
-      </c>
-      <c r="G88" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H88" t="s">
-        <v>85</v>
-      </c>
-      <c r="J88" t="s">
-        <v>110</v>
-      </c>
-      <c r="M88" t="s">
-        <v>47</v>
-      </c>
-      <c r="O88" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="P88" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" s="3"/>
-      <c r="S88">
-        <v>60</v>
-      </c>
-      <c r="T88" s="2">
-        <v>140</v>
-      </c>
-      <c r="U88" s="3">
-        <v>10</v>
-      </c>
+      <c r="T88" s="2"/>
+      <c r="U88" s="3"/>
       <c r="W88" s="2"/>
       <c r="X88" s="3"/>
       <c r="Z88" s="2"/>
       <c r="AA88" s="3"/>
-    </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC88" s="2"/>
+      <c r="AD88" s="3"/>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>40</v>
       </c>
       <c r="B89" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C89" t="s">
         <v>94</v>
@@ -4847,7 +5106,7 @@
         <v>77</v>
       </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="H89" t="s">
         <v>85</v>
@@ -4867,7 +5126,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="3"/>
       <c r="S89">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="T89" s="2">
         <v>140</v>
@@ -4879,34 +5138,42 @@
       <c r="X89" s="3"/>
       <c r="Z89" s="2"/>
       <c r="AA89" s="3"/>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC89" s="2"/>
+      <c r="AD89" s="3"/>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>40</v>
       </c>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="E90" t="s">
         <v>36</v>
       </c>
       <c r="F90" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s">
         <v>28</v>
       </c>
+      <c r="H90" t="s">
+        <v>85</v>
+      </c>
       <c r="J90" t="s">
-        <v>46</v>
-      </c>
-      <c r="N90" t="s">
-        <v>30</v>
+        <v>110</v>
+      </c>
+      <c r="M90" t="s">
+        <v>47</v>
+      </c>
+      <c r="O90" t="s">
+        <v>78</v>
       </c>
       <c r="P90" t="s">
         <v>31</v>
@@ -4917,42 +5184,102 @@
         <v>90</v>
       </c>
       <c r="T90" s="2">
+        <v>140</v>
+      </c>
+      <c r="U90" s="3">
         <v>10</v>
-      </c>
-      <c r="U90" s="3">
-        <v>145</v>
       </c>
       <c r="W90" s="2"/>
       <c r="X90" s="3"/>
       <c r="Z90" s="2"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC90" s="2"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C91" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="E91" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" t="s">
+        <v>27</v>
+      </c>
+      <c r="G91" t="s">
+        <v>28</v>
+      </c>
+      <c r="J91" t="s">
+        <v>46</v>
+      </c>
+      <c r="N91" t="s">
+        <v>30</v>
       </c>
       <c r="P91" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" s="3"/>
-      <c r="T91" s="2"/>
-      <c r="U91" s="3"/>
+      <c r="S91">
+        <v>90</v>
+      </c>
+      <c r="T91" s="2">
+        <v>10</v>
+      </c>
+      <c r="U91" s="3">
+        <v>145</v>
+      </c>
       <c r="W91" s="2"/>
       <c r="X91" s="3"/>
       <c r="Z91" s="2"/>
       <c r="AA91" s="3"/>
+      <c r="AC91" s="2"/>
+      <c r="AD91" s="3"/>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" t="s">
+        <v>164</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>35</v>
+      </c>
+      <c r="P92" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="3"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="3"/>
+      <c r="W92" s="2"/>
+      <c r="X92" s="3"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="5"/>
+      <c r="AC92" s="2"/>
+      <c r="AD92" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W1:Y1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AC1:AE1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCCC1AB-8488-478B-A1DE-BC5E5227C5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B129CB1B-A380-4C0B-9884-7FF98DC17316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -600,6 +600,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -648,6 +654,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -980,31 +987,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8" t="s">
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8" t="s">
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8" t="s">
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8" t="s">
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1433,15 +1440,8 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="3"/>
-      <c r="S9">
-        <v>40</v>
-      </c>
-      <c r="T9" s="2">
-        <v>10</v>
-      </c>
-      <c r="U9" s="3">
-        <v>145</v>
-      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="3"/>
       <c r="W9" s="2"/>
       <c r="X9" s="3"/>
       <c r="Z9" s="2"/>
@@ -1870,7 +1870,7 @@
       <c r="A19" t="s">
         <v>82</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="8" t="s">
         <v>75</v>
       </c>
       <c r="C19" t="s">
@@ -1919,7 +1919,7 @@
       <c r="A20" t="s">
         <v>83</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="8" t="s">
         <v>75</v>
       </c>
       <c r="C20" t="s">
@@ -2002,10 +2002,16 @@
       </c>
       <c r="W21" s="2"/>
       <c r="X21" s="3"/>
+      <c r="Y21">
+        <v>0</v>
+      </c>
       <c r="Z21" s="2"/>
       <c r="AA21" s="3"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="3"/>
+      <c r="AE21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -2020,6 +2026,7 @@
       <c r="D22" t="s">
         <v>76</v>
       </c>
+      <c r="E22" s="7"/>
       <c r="F22" t="s">
         <v>77</v>
       </c>
@@ -2115,7 +2122,7 @@
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C24" t="s">
@@ -2151,7 +2158,7 @@
       <c r="A25" t="s">
         <v>82</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C25" t="s">
@@ -2187,7 +2194,7 @@
       <c r="A26" t="s">
         <v>83</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C26" t="s">
@@ -2226,7 +2233,7 @@
       <c r="B27" t="s">
         <v>89</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D27" t="s">
@@ -2265,7 +2272,7 @@
       <c r="B28" t="s">
         <v>89</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D28" t="s">
@@ -2295,7 +2302,7 @@
       <c r="B29" t="s">
         <v>89</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D29" t="s">
@@ -2325,7 +2332,7 @@
       <c r="B30" t="s">
         <v>89</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D30" t="s">
@@ -2379,20 +2386,26 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="3"/>
       <c r="S31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" s="2">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="U31" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W31" s="2"/>
       <c r="X31" s="3"/>
       <c r="Z31" s="2"/>
       <c r="AA31" s="3"/>
+      <c r="AB31">
+        <v>0</v>
+      </c>
       <c r="AC31" s="2"/>
       <c r="AD31" s="3"/>
+      <c r="AE31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -2419,22 +2432,28 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="3"/>
       <c r="S32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" s="2">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="U32" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W32" s="2"/>
       <c r="X32" s="3"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="5"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32">
+        <v>0</v>
+      </c>
       <c r="AC32" s="2"/>
       <c r="AD32" s="3"/>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -2485,8 +2504,11 @@
       <c r="AA33" s="3"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="3"/>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE33">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2538,7 +2560,7 @@
       <c r="AC34" s="2"/>
       <c r="AD34" s="3"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -2590,7 +2612,7 @@
       <c r="AC35" s="2"/>
       <c r="AD35" s="3"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2642,7 +2664,7 @@
       <c r="AC36" s="2"/>
       <c r="AD36" s="3"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>55</v>
       </c>
@@ -2691,7 +2713,7 @@
       <c r="AC37" s="2"/>
       <c r="AD37" s="3"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -2741,7 +2763,7 @@
       <c r="AC38" s="2"/>
       <c r="AD38" s="3"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2785,7 +2807,7 @@
       <c r="AC39" s="2"/>
       <c r="AD39" s="3"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -2829,7 +2851,7 @@
       <c r="AC40" s="2"/>
       <c r="AD40" s="3"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2868,7 +2890,7 @@
       <c r="AC41" s="2"/>
       <c r="AD41" s="3"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2898,7 +2920,7 @@
       <c r="AC42" s="2"/>
       <c r="AD42" s="3"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>83</v>
       </c>
@@ -2928,7 +2950,7 @@
       <c r="AC43" s="2"/>
       <c r="AD43" s="3"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -2964,7 +2986,7 @@
       <c r="AC44" s="2"/>
       <c r="AD44" s="3"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -3013,7 +3035,7 @@
       <c r="AC45" s="2"/>
       <c r="AD45" s="3"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -3062,7 +3084,7 @@
       <c r="AC46" s="2"/>
       <c r="AD46" s="3"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3114,7 +3136,7 @@
       <c r="AC47" s="2"/>
       <c r="AD47" s="3"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B129CB1B-A380-4C0B-9884-7FF98DC17316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5BFB3B-51E3-43AF-A84F-2B225809888A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5BFB3B-51E3-43AF-A84F-2B225809888A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BA7A32-0453-4F24-93FB-9FDF46E14124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebungen" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="178">
   <si>
     <t>Kombi</t>
   </si>
@@ -86,9 +99,6 @@
   </si>
   <si>
     <t>elbow_flex_fix</t>
-  </si>
-  <si>
-    <t>Notizen</t>
   </si>
   <si>
     <t>Free + Cable</t>
@@ -966,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF92"/>
+  <dimension ref="A1:AI92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -984,36 +994,39 @@
     <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="8.21875" customWidth="1"/>
     <col min="29" max="31" width="8.21875" customWidth="1"/>
+    <col min="32" max="32" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q1" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
       <c r="T1" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
       <c r="W1" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
       <c r="Z1" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA1" s="9"/>
       <c r="AB1" s="9"/>
       <c r="AC1" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD1" s="9"/>
       <c r="AE1" s="9"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,63 +1094,61 @@
         <v>21</v>
       </c>
       <c r="W2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="Z2" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>173</v>
-      </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AD2" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AE2" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="AE2" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="1"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>31</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
@@ -1162,31 +1173,47 @@
       <c r="AE3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF3" t="str">
+        <f>A3</f>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG3" t="str">
+        <f t="shared" ref="AG3:AI3" si="0">B3</f>
+        <v>Bayesian curl</v>
+      </c>
+      <c r="AH3" t="str">
+        <f t="shared" si="0"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI3" t="str">
+        <f t="shared" si="0"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>35</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
+      <c r="P4" t="s">
         <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>39</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="3"/>
@@ -1198,40 +1225,56 @@
       <c r="AA4" s="3"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="3"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF4" t="str">
+        <f t="shared" ref="AF4:AF67" si="1">A4</f>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG4" t="str">
+        <f t="shared" ref="AG4:AG67" si="2">B4</f>
+        <v>Romanian Deadlift</v>
+      </c>
+      <c r="AH4" t="str">
+        <f t="shared" ref="AH4:AH67" si="3">C4</f>
+        <v>legs</v>
+      </c>
+      <c r="AI4" t="str">
+        <f t="shared" ref="AI4:AI67" si="4">D4</f>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>46</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>47</v>
       </c>
-      <c r="N5" t="s">
-        <v>48</v>
-      </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
@@ -1256,37 +1299,53 @@
       <c r="AE5">
         <v>-45</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF5" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG5" t="str">
+        <f t="shared" si="2"/>
+        <v>Y raise</v>
+      </c>
+      <c r="AH5" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI5" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>51</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P6" t="s">
         <v>53</v>
-      </c>
-      <c r="N6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" t="s">
-        <v>54</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="3"/>
@@ -1312,34 +1371,50 @@
       <c r="AE6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF6" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG6" t="str">
+        <f t="shared" si="2"/>
+        <v>archer pull</v>
+      </c>
+      <c r="AH6" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI6" t="str">
+        <f t="shared" si="4"/>
+        <v>raw</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="M7" t="s">
         <v>57</v>
       </c>
-      <c r="M7" t="s">
-        <v>58</v>
-      </c>
       <c r="P7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="3"/>
@@ -1365,34 +1440,50 @@
       <c r="AE7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF7" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG7" t="str">
+        <f t="shared" si="2"/>
+        <v>archer pull</v>
+      </c>
+      <c r="AH7" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI7" t="str">
+        <f t="shared" si="4"/>
+        <v>raw</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
         <v>60</v>
       </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="2">
         <v>30</v>
@@ -1412,31 +1503,47 @@
       <c r="AA8" s="3"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="3"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF8" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG8" t="str">
+        <f t="shared" si="2"/>
+        <v>back row</v>
+      </c>
+      <c r="AH8" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI8" t="str">
+        <f t="shared" si="4"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>64</v>
-      </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="3"/>
@@ -1448,22 +1555,38 @@
       <c r="AA9" s="3"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="3"/>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF9" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG9" t="str">
+        <f t="shared" si="2"/>
+        <v>concentration curl</v>
+      </c>
+      <c r="AH9" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI9" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="3"/>
@@ -1475,37 +1598,53 @@
       <c r="AA10" s="3"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="3"/>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF10" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG10" t="str">
+        <f t="shared" si="2"/>
+        <v>core</v>
+      </c>
+      <c r="AH10" t="str">
+        <f t="shared" si="3"/>
+        <v>core</v>
+      </c>
+      <c r="AI10" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
         <v>66</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>67</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>68</v>
       </c>
-      <c r="K11" t="s">
-        <v>69</v>
-      </c>
       <c r="P11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="3"/>
@@ -1530,28 +1669,44 @@
       <c r="AE11">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF11" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG11" t="str">
+        <f t="shared" si="2"/>
+        <v>crossbody curl</v>
+      </c>
+      <c r="AH11" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI11" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" t="s">
         <v>71</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="3"/>
@@ -1563,28 +1718,44 @@
       <c r="AA12" s="5"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="3"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF12" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull</v>
+      </c>
+      <c r="AG12" t="str">
+        <f t="shared" si="2"/>
+        <v>crunch</v>
+      </c>
+      <c r="AH12" t="str">
+        <f t="shared" si="3"/>
+        <v>abs</v>
+      </c>
+      <c r="AI12" t="str">
+        <f t="shared" si="4"/>
+        <v>ropes</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
         <v>71</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>72</v>
       </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
@@ -1596,37 +1767,53 @@
       <c r="AA13" s="3"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="3"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF13" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull2</v>
+      </c>
+      <c r="AG13" t="str">
+        <f t="shared" si="2"/>
+        <v>crunch</v>
+      </c>
+      <c r="AH13" t="str">
+        <f t="shared" si="3"/>
+        <v>abs</v>
+      </c>
+      <c r="AI13" t="str">
+        <f t="shared" si="4"/>
+        <v>ropes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
         <v>76</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
         <v>77</v>
       </c>
-      <c r="I14" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="P14" t="s">
         <v>30</v>
-      </c>
-      <c r="O14" t="s">
-        <v>78</v>
-      </c>
-      <c r="P14" t="s">
-        <v>31</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
@@ -1651,37 +1838,53 @@
       <c r="AE14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF14" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG14" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH14" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI14" t="str">
+        <f t="shared" si="4"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
         <v>43</v>
       </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>44</v>
-      </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" t="s">
         <v>46</v>
       </c>
-      <c r="M15" t="s">
-        <v>47</v>
-      </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
@@ -1706,37 +1909,53 @@
       <c r="AE15">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF15" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG15" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH15" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI15" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
         <v>25</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
         <v>28</v>
       </c>
-      <c r="I16" t="s">
-        <v>29</v>
-      </c>
       <c r="M16" t="s">
+        <v>78</v>
+      </c>
+      <c r="O16" t="s">
         <v>79</v>
       </c>
-      <c r="O16" t="s">
-        <v>80</v>
-      </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="3"/>
@@ -1761,34 +1980,50 @@
       <c r="AE16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF16" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG16" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH16" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI16" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" t="s">
         <v>27</v>
       </c>
-      <c r="G17" t="s">
-        <v>28</v>
-      </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="3"/>
@@ -1813,34 +2048,50 @@
       <c r="AE17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF17" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull</v>
+      </c>
+      <c r="AG17" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH17" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI17" t="str">
+        <f t="shared" si="4"/>
+        <v>straight</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
         <v>27</v>
       </c>
-      <c r="G18" t="s">
-        <v>28</v>
-      </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="3"/>
@@ -1865,34 +2116,50 @@
       <c r="AE18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF18" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull2</v>
+      </c>
+      <c r="AG18" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH18" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI18" t="str">
+        <f t="shared" si="4"/>
+        <v>straight</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="3"/>
@@ -1914,34 +2181,50 @@
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF19" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG19" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH19" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI19" t="str">
+        <f t="shared" si="4"/>
+        <v>straight</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="3"/>
@@ -1960,34 +2243,50 @@
       <c r="AA20" s="3"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="3"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF20" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG20" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH20" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI20" t="str">
+        <f t="shared" si="4"/>
+        <v>straight</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" t="s">
         <v>84</v>
       </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" t="s">
-        <v>85</v>
-      </c>
       <c r="P21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="3"/>
@@ -2012,38 +2311,54 @@
       <c r="AE21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF21" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG21" t="str">
+        <f t="shared" si="2"/>
+        <v>curl</v>
+      </c>
+      <c r="AH21" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI21" t="str">
+        <f t="shared" si="4"/>
+        <v>EZ bar</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" t="s">
         <v>28</v>
-      </c>
-      <c r="I22" t="s">
-        <v>29</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="3"/>
@@ -2062,43 +2377,59 @@
       <c r="AA22" s="5"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="3"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF22" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG22" t="str">
+        <f t="shared" si="2"/>
+        <v>curl (0)</v>
+      </c>
+      <c r="AH22" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI22" t="str">
+        <f t="shared" si="4"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
         <v>76</v>
       </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" t="s">
+        <v>78</v>
+      </c>
+      <c r="N23" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" t="s">
         <v>77</v>
       </c>
-      <c r="G23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" t="s">
-        <v>79</v>
-      </c>
-      <c r="N23" t="s">
-        <v>79</v>
-      </c>
-      <c r="O23" t="s">
-        <v>78</v>
-      </c>
       <c r="P23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="3"/>
@@ -2117,31 +2448,47 @@
       <c r="AA23" s="3"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="3"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF23" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG23" t="str">
+        <f t="shared" si="2"/>
+        <v>curl (sag)</v>
+      </c>
+      <c r="AH23" t="str">
+        <f t="shared" si="3"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI23" t="str">
+        <f t="shared" si="4"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
         <v>60</v>
       </c>
-      <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
       <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" t="s">
         <v>38</v>
-      </c>
-      <c r="P24" t="s">
-        <v>39</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" s="3"/>
@@ -2153,31 +2500,47 @@
       <c r="AA24" s="3"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="3"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF24" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG24" t="str">
+        <f t="shared" si="2"/>
+        <v>deadlift</v>
+      </c>
+      <c r="AH24" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI24" t="str">
+        <f t="shared" si="4"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
         <v>89</v>
       </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
       <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" t="s">
         <v>36</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>37</v>
       </c>
-      <c r="H25" t="s">
+      <c r="P25" t="s">
         <v>38</v>
-      </c>
-      <c r="P25" t="s">
-        <v>39</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" s="3"/>
@@ -2189,31 +2552,47 @@
       <c r="AA25" s="3"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="3"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF25" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG25" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH25" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI25" t="str">
+        <f t="shared" si="4"/>
+        <v>long light bend</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
-        <v>90</v>
-      </c>
       <c r="E26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" t="s">
         <v>36</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>37</v>
       </c>
-      <c r="H26" t="s">
+      <c r="P26" t="s">
         <v>38</v>
-      </c>
-      <c r="P26" t="s">
-        <v>39</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" s="3"/>
@@ -2225,34 +2604,50 @@
       <c r="AA26" s="3"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="3"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF26" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG26" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH26" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI26" t="str">
+        <f t="shared" si="4"/>
+        <v>long light bend</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" t="s">
         <v>91</v>
       </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" t="s">
-        <v>92</v>
-      </c>
       <c r="N27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" s="3"/>
@@ -2264,25 +2659,41 @@
       <c r="AA27" s="5"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="3"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF27" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG27" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH27" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI27" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" s="3"/>
@@ -2294,25 +2705,41 @@
       <c r="AA28" s="3"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="3"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF28" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG28" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH28" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI28" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" s="3"/>
@@ -2324,31 +2751,47 @@
       <c r="AA29" s="3"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="3"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF29" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG29" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH29" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI29" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
         <v>35</v>
       </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H30" t="s">
+        <v>37</v>
+      </c>
+      <c r="P30" t="s">
         <v>38</v>
-      </c>
-      <c r="P30" t="s">
-        <v>39</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" s="3"/>
@@ -2360,28 +2803,44 @@
       <c r="AA30" s="3"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="3"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF30" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG30" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH30" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI30" t="str">
+        <f t="shared" si="4"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s">
         <v>94</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>95</v>
       </c>
-      <c r="F31" t="s">
-        <v>96</v>
-      </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="3"/>
@@ -2406,28 +2865,44 @@
       <c r="AE31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF31" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull</v>
+      </c>
+      <c r="AG31" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH31" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI31" t="str">
+        <f t="shared" si="4"/>
+        <v>cuff</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" t="s">
         <v>94</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>95</v>
       </c>
-      <c r="F32" t="s">
-        <v>96</v>
-      </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" s="3"/>
@@ -2452,40 +2927,56 @@
       <c r="AE32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF32" t="str">
+        <f t="shared" si="1"/>
+        <v>Lat pull2</v>
+      </c>
+      <c r="AG32" t="str">
+        <f t="shared" si="2"/>
+        <v>extension</v>
+      </c>
+      <c r="AH32" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI32" t="str">
+        <f t="shared" si="4"/>
+        <v>cuff</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
         <v>97</v>
       </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>98</v>
-      </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="3"/>
@@ -2502,45 +2993,64 @@
       <c r="X33" s="3"/>
       <c r="Z33" s="2"/>
       <c r="AA33" s="3"/>
+      <c r="AB33">
+        <v>0</v>
+      </c>
       <c r="AC33" s="2"/>
       <c r="AD33" s="3"/>
       <c r="AE33">
         <v>-45</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF33" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG33" t="str">
+        <f t="shared" si="2"/>
+        <v>extension (l-s)</v>
+      </c>
+      <c r="AH33" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI33" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" t="s">
+        <v>67</v>
+      </c>
+      <c r="K34" t="s">
         <v>99</v>
       </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" t="s">
-        <v>68</v>
-      </c>
-      <c r="K34" t="s">
-        <v>100</v>
-      </c>
       <c r="O34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="3"/>
@@ -2548,51 +3058,73 @@
         <v>20</v>
       </c>
       <c r="T34" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="U34" s="3">
         <v>5</v>
       </c>
       <c r="W34" s="2"/>
       <c r="X34" s="3"/>
+      <c r="Y34">
+        <v>0</v>
+      </c>
       <c r="Z34" s="2"/>
       <c r="AA34" s="3"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="3"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AE34">
+        <v>-90</v>
+      </c>
+      <c r="AF34" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG34" t="str">
+        <f t="shared" si="2"/>
+        <v>extension (lat)</v>
+      </c>
+      <c r="AH34" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI34" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" t="s">
         <v>67</v>
       </c>
-      <c r="I35" t="s">
-        <v>68</v>
-      </c>
       <c r="M35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" s="3"/>
@@ -2600,51 +3132,73 @@
         <v>20</v>
       </c>
       <c r="T35" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="U35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W35" s="2"/>
       <c r="X35" s="3"/>
+      <c r="Y35">
+        <v>0</v>
+      </c>
       <c r="Z35" s="2"/>
       <c r="AA35" s="3"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="3"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AE35">
+        <v>-90</v>
+      </c>
+      <c r="AF35" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG35" t="str">
+        <f t="shared" si="2"/>
+        <v>extension (lat)</v>
+      </c>
+      <c r="AH35" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI35" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" s="3"/>
@@ -2663,37 +3217,56 @@
       <c r="AA36" s="3"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="3"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG36" t="str">
+        <f t="shared" si="2"/>
+        <v>extension (sag)</v>
+      </c>
+      <c r="AH36" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI36" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" t="s">
         <v>94</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>95</v>
       </c>
-      <c r="F37" t="s">
-        <v>96</v>
-      </c>
       <c r="G37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" s="3"/>
@@ -2712,37 +3285,53 @@
       <c r="AA37" s="5"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="3"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF37" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG37" t="str">
+        <f t="shared" si="2"/>
+        <v>extension (sag)</v>
+      </c>
+      <c r="AH37" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI37" t="str">
+        <f t="shared" si="4"/>
+        <v>cuff</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q38" s="2">
         <v>0</v>
@@ -2762,31 +3351,47 @@
       <c r="AA38" s="3"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="3"/>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF38" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG38" t="str">
+        <f t="shared" si="2"/>
+        <v>face pull</v>
+      </c>
+      <c r="AH38" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI38" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" t="s">
         <v>102</v>
       </c>
-      <c r="C39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" t="s">
-        <v>51</v>
-      </c>
-      <c r="G39" t="s">
-        <v>103</v>
-      </c>
       <c r="P39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q39" s="2">
         <v>0</v>
@@ -2806,31 +3411,47 @@
       <c r="AA39" s="3"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF39" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG39" t="str">
+        <f t="shared" si="2"/>
+        <v>face pull</v>
+      </c>
+      <c r="AH39" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI39" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" t="s">
         <v>102</v>
       </c>
-      <c r="C40" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" t="s">
-        <v>103</v>
-      </c>
       <c r="P40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q40" s="2">
         <v>0</v>
@@ -2850,34 +3471,50 @@
       <c r="AA40" s="3"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF40" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG40" t="str">
+        <f t="shared" si="2"/>
+        <v>face pull</v>
+      </c>
+      <c r="AH40" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI40" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" t="s">
         <v>91</v>
       </c>
-      <c r="D41" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-      <c r="G41" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" t="s">
-        <v>92</v>
-      </c>
       <c r="N41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="3"/>
@@ -2889,25 +3526,41 @@
       <c r="AA41" s="3"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="3"/>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF41" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG41" t="str">
+        <f t="shared" si="2"/>
+        <v>flexion</v>
+      </c>
+      <c r="AH41" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI41" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="3"/>
@@ -2919,25 +3572,41 @@
       <c r="AA42" s="5"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="3"/>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF42" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG42" t="str">
+        <f t="shared" si="2"/>
+        <v>flexion</v>
+      </c>
+      <c r="AH42" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI42" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" s="3"/>
@@ -2949,31 +3618,47 @@
       <c r="AA43" s="3"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="3"/>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF43" t="str">
+        <f t="shared" si="1"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG43" t="str">
+        <f t="shared" si="2"/>
+        <v>flexion</v>
+      </c>
+      <c r="AH43" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI43" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" t="s">
         <v>35</v>
       </c>
-      <c r="E44" t="s">
-        <v>36</v>
-      </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H44" t="s">
+        <v>37</v>
+      </c>
+      <c r="P44" t="s">
         <v>38</v>
-      </c>
-      <c r="P44" t="s">
-        <v>39</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" s="3"/>
@@ -2985,37 +3670,53 @@
       <c r="AA44" s="3"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="3"/>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF44" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG44" t="str">
+        <f t="shared" si="2"/>
+        <v>flexion</v>
+      </c>
+      <c r="AH44" t="str">
+        <f t="shared" si="3"/>
+        <v>forearm</v>
+      </c>
+      <c r="AI44" t="str">
+        <f t="shared" si="4"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" t="s">
         <v>105</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
         <v>106</v>
       </c>
-      <c r="D45" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
         <v>107</v>
       </c>
-      <c r="I45" t="s">
-        <v>108</v>
-      </c>
       <c r="K45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q45" s="2">
         <v>25</v>
@@ -3034,37 +3735,53 @@
       <c r="AA45" s="3"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="3"/>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF45" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG45" t="str">
+        <f t="shared" si="2"/>
+        <v>fly</v>
+      </c>
+      <c r="AH45" t="str">
+        <f t="shared" si="3"/>
+        <v>chest</v>
+      </c>
+      <c r="AI45" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" t="s">
         <v>105</v>
       </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G46" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46" t="s">
         <v>109</v>
       </c>
-      <c r="J46" t="s">
-        <v>110</v>
-      </c>
       <c r="M46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q46" s="2">
         <v>25</v>
@@ -3083,40 +3800,56 @@
       <c r="AA46" s="3"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="3"/>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF46" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG46" t="str">
+        <f t="shared" si="2"/>
+        <v>fly</v>
+      </c>
+      <c r="AH46" t="str">
+        <f t="shared" si="3"/>
+        <v>chest</v>
+      </c>
+      <c r="AI46" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" t="s">
+        <v>102</v>
+      </c>
+      <c r="I47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M47" t="s">
         <v>111</v>
       </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" t="s">
-        <v>36</v>
-      </c>
-      <c r="F47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G47" t="s">
-        <v>103</v>
-      </c>
-      <c r="I47" t="s">
-        <v>29</v>
-      </c>
-      <c r="M47" t="s">
+      <c r="O47" t="s">
         <v>112</v>
       </c>
-      <c r="O47" t="s">
-        <v>113</v>
-      </c>
       <c r="P47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q47" s="2">
         <v>25</v>
@@ -3135,40 +3868,56 @@
       <c r="AA47" s="5"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="3"/>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF47" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG47" t="str">
+        <f t="shared" si="2"/>
+        <v>fly (t-l/1-8)</v>
+      </c>
+      <c r="AH47" t="str">
+        <f t="shared" si="3"/>
+        <v>chest</v>
+      </c>
+      <c r="AI47" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
         <v>114</v>
       </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" t="s">
-        <v>115</v>
-      </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M48" t="s">
+        <v>111</v>
+      </c>
+      <c r="O48" t="s">
         <v>112</v>
       </c>
-      <c r="O48" t="s">
-        <v>113</v>
-      </c>
       <c r="P48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q48" s="2">
         <v>25</v>
@@ -3187,40 +3936,56 @@
       <c r="AA48" s="3"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="3"/>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF48" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG48" t="str">
+        <f t="shared" si="2"/>
+        <v>fly (t-l/16-22)</v>
+      </c>
+      <c r="AH48" t="str">
+        <f t="shared" si="3"/>
+        <v>chest</v>
+      </c>
+      <c r="AI48" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q49" s="2">
         <v>25</v>
@@ -3239,37 +4004,53 @@
       <c r="AA49" s="3"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="3"/>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF49" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG49" t="str">
+        <f t="shared" si="2"/>
+        <v>fly (trans)</v>
+      </c>
+      <c r="AH49" t="str">
+        <f t="shared" si="3"/>
+        <v>chest</v>
+      </c>
+      <c r="AI49" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" t="s">
         <v>117</v>
       </c>
-      <c r="C50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D50" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" t="s">
         <v>118</v>
       </c>
-      <c r="F50" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" t="s">
-        <v>119</v>
-      </c>
       <c r="P50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q50" s="2">
         <v>0</v>
@@ -3288,43 +4069,59 @@
       <c r="AA50" s="3"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="3"/>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF50" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG50" t="str">
+        <f t="shared" si="2"/>
+        <v>front raise</v>
+      </c>
+      <c r="AH50" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI50" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
         <v>117</v>
       </c>
-      <c r="C51" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" t="s">
-        <v>43</v>
-      </c>
-      <c r="E51" t="s">
-        <v>118</v>
-      </c>
       <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" t="s">
         <v>120</v>
       </c>
-      <c r="G51" t="s">
-        <v>28</v>
-      </c>
-      <c r="H51" t="s">
-        <v>38</v>
-      </c>
-      <c r="J51" t="s">
-        <v>121</v>
-      </c>
       <c r="M51" t="s">
+        <v>46</v>
+      </c>
+      <c r="N51" t="s">
         <v>47</v>
       </c>
-      <c r="N51" t="s">
-        <v>48</v>
-      </c>
       <c r="P51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q51" s="2">
         <v>0</v>
@@ -3343,37 +4140,53 @@
       <c r="AA51" s="3"/>
       <c r="AC51" s="2"/>
       <c r="AD51" s="3"/>
-    </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF51" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG51" t="str">
+        <f t="shared" si="2"/>
+        <v>front raise</v>
+      </c>
+      <c r="AH51" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI51" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" t="s">
         <v>28</v>
-      </c>
-      <c r="I52" t="s">
-        <v>29</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q52" s="2">
         <v>0</v>
@@ -3392,34 +4205,50 @@
       <c r="AA52" s="5"/>
       <c r="AC52" s="2"/>
       <c r="AD52" s="3"/>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF52" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG52" t="str">
+        <f t="shared" si="2"/>
+        <v>front raise</v>
+      </c>
+      <c r="AH52" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI52" t="str">
+        <f t="shared" si="4"/>
+        <v>ropes</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" t="s">
         <v>117</v>
       </c>
-      <c r="C53" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" t="s">
-        <v>118</v>
-      </c>
       <c r="F53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q53" s="2">
         <v>0</v>
@@ -3438,37 +4267,53 @@
       <c r="AA53" s="3"/>
       <c r="AC53" s="2"/>
       <c r="AD53" s="3"/>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF53" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG53" t="str">
+        <f t="shared" si="2"/>
+        <v>front raise</v>
+      </c>
+      <c r="AH53" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI53" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q54" s="2">
         <v>0</v>
@@ -3488,31 +4333,47 @@
       <c r="AA54" s="3"/>
       <c r="AC54" s="2"/>
       <c r="AD54" s="3"/>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF54" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG54" t="str">
+        <f t="shared" si="2"/>
+        <v>front row</v>
+      </c>
+      <c r="AH54" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI54" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
         <v>123</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>124</v>
       </c>
-      <c r="D55" t="s">
-        <v>125</v>
-      </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s">
+        <v>37</v>
+      </c>
+      <c r="P55" t="s">
         <v>38</v>
-      </c>
-      <c r="P55" t="s">
-        <v>39</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" s="3"/>
@@ -3524,40 +4385,56 @@
       <c r="AA55" s="3"/>
       <c r="AC55" s="2"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF55" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG55" t="str">
+        <f t="shared" si="2"/>
+        <v>hyperextension</v>
+      </c>
+      <c r="AH55" t="str">
+        <f t="shared" si="3"/>
+        <v>glute</v>
+      </c>
+      <c r="AI55" t="str">
+        <f t="shared" si="4"/>
+        <v>plates</v>
+      </c>
+    </row>
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" t="s">
+        <v>42</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56" t="s">
         <v>126</v>
       </c>
-      <c r="C56" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" t="s">
-        <v>43</v>
-      </c>
-      <c r="E56" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" t="s">
-        <v>127</v>
-      </c>
       <c r="G56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H56" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" t="s">
+        <v>45</v>
+      </c>
+      <c r="N56" t="s">
+        <v>29</v>
+      </c>
+      <c r="P56" t="s">
         <v>38</v>
-      </c>
-      <c r="J56" t="s">
-        <v>46</v>
-      </c>
-      <c r="N56" t="s">
-        <v>30</v>
-      </c>
-      <c r="P56" t="s">
-        <v>39</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" s="3"/>
@@ -3569,34 +4446,50 @@
       <c r="AA56" s="3"/>
       <c r="AC56" s="2"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF56" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG56" t="str">
+        <f t="shared" si="2"/>
+        <v>kelso shrugg</v>
+      </c>
+      <c r="AH56" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI56" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" t="s">
         <v>67</v>
       </c>
-      <c r="I57" t="s">
-        <v>68</v>
-      </c>
       <c r="M57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q57" s="2">
         <v>30</v>
@@ -3615,34 +4508,50 @@
       <c r="AA57" s="5"/>
       <c r="AC57" s="2"/>
       <c r="AD57" s="3"/>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF57" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG57" t="str">
+        <f t="shared" si="2"/>
+        <v>kenan flap</v>
+      </c>
+      <c r="AH57" t="str">
+        <f t="shared" si="3"/>
+        <v>back</v>
+      </c>
+      <c r="AI57" t="str">
+        <f t="shared" si="4"/>
+        <v>cuff</v>
+      </c>
+    </row>
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" t="s">
         <v>129</v>
       </c>
-      <c r="C58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D58" t="s">
-        <v>93</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
+        <v>66</v>
+      </c>
+      <c r="I58" t="s">
         <v>130</v>
       </c>
-      <c r="G58" t="s">
-        <v>67</v>
-      </c>
-      <c r="I58" t="s">
-        <v>131</v>
-      </c>
       <c r="K58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q58" s="2">
         <v>0</v>
@@ -3661,34 +4570,50 @@
       <c r="AA58" s="3"/>
       <c r="AC58" s="2"/>
       <c r="AD58" s="3"/>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF58" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG58" t="str">
+        <f t="shared" si="2"/>
+        <v>lateral raise</v>
+      </c>
+      <c r="AH58" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI58" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" t="s">
+        <v>35</v>
+      </c>
+      <c r="F59" t="s">
         <v>129</v>
       </c>
-      <c r="C59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" t="s">
-        <v>43</v>
-      </c>
-      <c r="E59" t="s">
-        <v>36</v>
-      </c>
-      <c r="F59" t="s">
-        <v>130</v>
-      </c>
       <c r="G59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q59" s="2">
         <v>0</v>
@@ -3707,31 +4632,47 @@
       <c r="AA59" s="3"/>
       <c r="AC59" s="2"/>
       <c r="AD59" s="3"/>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF59" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG59" t="str">
+        <f t="shared" si="2"/>
+        <v>lateral raise</v>
+      </c>
+      <c r="AH59" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI59" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" t="s">
+        <v>35</v>
+      </c>
+      <c r="F60" t="s">
         <v>129</v>
       </c>
-      <c r="C60" t="s">
-        <v>42</v>
-      </c>
-      <c r="D60" t="s">
-        <v>43</v>
-      </c>
-      <c r="E60" t="s">
-        <v>36</v>
-      </c>
-      <c r="F60" t="s">
-        <v>130</v>
-      </c>
       <c r="G60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q60" s="2">
         <v>0</v>
@@ -3750,37 +4691,53 @@
       <c r="AA60" s="3"/>
       <c r="AC60" s="2"/>
       <c r="AD60" s="3"/>
-    </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF60" t="str">
+        <f t="shared" si="1"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG60" t="str">
+        <f t="shared" si="2"/>
+        <v>lateral raise</v>
+      </c>
+      <c r="AH60" t="str">
+        <f t="shared" si="3"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI60" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" t="s">
+        <v>126</v>
+      </c>
+      <c r="H61" t="s">
         <v>132</v>
       </c>
-      <c r="C61" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" t="s">
-        <v>127</v>
-      </c>
-      <c r="H61" t="s">
-        <v>133</v>
-      </c>
       <c r="J61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="3"/>
@@ -3799,40 +4756,56 @@
       <c r="AA61" s="3"/>
       <c r="AC61" s="2"/>
       <c r="AD61" s="3"/>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF61" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG61" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension</v>
+      </c>
+      <c r="AH61" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI61" t="str">
+        <f t="shared" si="4"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K62" t="s">
+        <v>29</v>
+      </c>
+      <c r="O62" t="s">
+        <v>77</v>
+      </c>
+      <c r="P62" t="s">
         <v>30</v>
-      </c>
-      <c r="O62" t="s">
-        <v>78</v>
-      </c>
-      <c r="P62" t="s">
-        <v>31</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="3"/>
@@ -3851,43 +4824,59 @@
       <c r="AA62" s="5"/>
       <c r="AC62" s="2"/>
       <c r="AD62" s="3"/>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF62" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG62" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (l-s)</v>
+      </c>
+      <c r="AH62" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI62" t="str">
+        <f t="shared" si="4"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D63" t="s">
         <v>134</v>
       </c>
-      <c r="C63" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" t="s">
-        <v>135</v>
-      </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F63" t="s">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H63" t="s">
+        <v>84</v>
+      </c>
+      <c r="J63" t="s">
+        <v>120</v>
+      </c>
+      <c r="M63" t="s">
+        <v>46</v>
+      </c>
+      <c r="O63" t="s">
         <v>77</v>
       </c>
-      <c r="G63" t="s">
-        <v>45</v>
-      </c>
-      <c r="H63" t="s">
-        <v>85</v>
-      </c>
-      <c r="J63" t="s">
-        <v>121</v>
-      </c>
-      <c r="M63" t="s">
-        <v>47</v>
-      </c>
-      <c r="O63" t="s">
-        <v>78</v>
-      </c>
       <c r="P63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="3"/>
@@ -3906,37 +4895,53 @@
       <c r="AA63" s="3"/>
       <c r="AC63" s="2"/>
       <c r="AD63" s="3"/>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF63" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG63" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (l-s)</v>
+      </c>
+      <c r="AH63" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI63" t="str">
+        <f t="shared" si="4"/>
+        <v>ez bar</v>
+      </c>
+    </row>
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D64" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" t="s">
+        <v>35</v>
+      </c>
+      <c r="F64" t="s">
         <v>76</v>
       </c>
-      <c r="E64" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
+        <v>44</v>
+      </c>
+      <c r="M64" t="s">
+        <v>78</v>
+      </c>
+      <c r="O64" t="s">
         <v>77</v>
       </c>
-      <c r="G64" t="s">
-        <v>45</v>
-      </c>
-      <c r="M64" t="s">
-        <v>79</v>
-      </c>
-      <c r="O64" t="s">
-        <v>78</v>
-      </c>
       <c r="P64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="3"/>
@@ -3955,40 +4960,56 @@
       <c r="AA64" s="3"/>
       <c r="AC64" s="2"/>
       <c r="AD64" s="3"/>
-    </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF64" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG64" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (l-s)</v>
+      </c>
+      <c r="AH64" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI64" t="str">
+        <f t="shared" si="4"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" t="s">
+        <v>117</v>
+      </c>
+      <c r="F65" t="s">
         <v>136</v>
       </c>
-      <c r="C65" t="s">
-        <v>94</v>
-      </c>
-      <c r="D65" t="s">
-        <v>93</v>
-      </c>
-      <c r="E65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
+        <v>66</v>
+      </c>
+      <c r="I65" t="s">
+        <v>56</v>
+      </c>
+      <c r="K65" t="s">
         <v>137</v>
       </c>
-      <c r="G65" t="s">
-        <v>67</v>
-      </c>
-      <c r="I65" t="s">
-        <v>57</v>
-      </c>
-      <c r="K65" t="s">
-        <v>138</v>
-      </c>
       <c r="O65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="3"/>
@@ -4007,43 +5028,59 @@
       <c r="AA65" s="3"/>
       <c r="AC65" s="2"/>
       <c r="AD65" s="3"/>
-    </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF65" t="str">
+        <f t="shared" si="1"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG65" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (lat)</v>
+      </c>
+      <c r="AH65" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI65" t="str">
+        <f t="shared" si="4"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F66" t="s">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s">
+        <v>66</v>
+      </c>
+      <c r="H66" t="s">
+        <v>132</v>
+      </c>
+      <c r="J66" t="s">
+        <v>120</v>
+      </c>
+      <c r="M66" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66" t="s">
         <v>77</v>
       </c>
-      <c r="G66" t="s">
-        <v>67</v>
-      </c>
-      <c r="H66" t="s">
-        <v>133</v>
-      </c>
-      <c r="J66" t="s">
-        <v>121</v>
-      </c>
-      <c r="M66" t="s">
-        <v>47</v>
-      </c>
-      <c r="O66" t="s">
-        <v>78</v>
-      </c>
       <c r="P66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="3"/>
@@ -4062,34 +5099,50 @@
       <c r="AA66" s="3"/>
       <c r="AC66" s="2"/>
       <c r="AD66" s="3"/>
-    </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF66" t="str">
+        <f t="shared" si="1"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG66" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (lat)</v>
+      </c>
+      <c r="AH66" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI66" t="str">
+        <f t="shared" si="4"/>
+        <v>ez bar</v>
+      </c>
+    </row>
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="3"/>
@@ -4108,40 +5161,56 @@
       <c r="AA67" s="5"/>
       <c r="AC67" s="2"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF67" t="str">
+        <f t="shared" si="1"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG67" t="str">
+        <f t="shared" si="2"/>
+        <v>overhead extension (lat)</v>
+      </c>
+      <c r="AH67" t="str">
+        <f t="shared" si="3"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI67" t="str">
+        <f t="shared" si="4"/>
+        <v>1rope</v>
+      </c>
+    </row>
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="3"/>
@@ -4160,43 +5229,59 @@
       <c r="AA68" s="3"/>
       <c r="AC68" s="2"/>
       <c r="AD68" s="3"/>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF68" t="str">
+        <f t="shared" ref="AF68:AF92" si="5">A68</f>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG68" t="str">
+        <f t="shared" ref="AG68:AG92" si="6">B68</f>
+        <v>overhead extension (sag)</v>
+      </c>
+      <c r="AH68" t="str">
+        <f t="shared" ref="AH68:AH92" si="7">C68</f>
+        <v>triceps</v>
+      </c>
+      <c r="AI68" t="str">
+        <f t="shared" ref="AI68:AI92" si="8">D68</f>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F69" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" t="s">
+        <v>84</v>
+      </c>
+      <c r="J69" t="s">
+        <v>120</v>
+      </c>
+      <c r="M69" t="s">
+        <v>46</v>
+      </c>
+      <c r="O69" t="s">
         <v>77</v>
       </c>
-      <c r="G69" t="s">
-        <v>28</v>
-      </c>
-      <c r="H69" t="s">
-        <v>85</v>
-      </c>
-      <c r="J69" t="s">
-        <v>121</v>
-      </c>
-      <c r="M69" t="s">
-        <v>47</v>
-      </c>
-      <c r="O69" t="s">
-        <v>78</v>
-      </c>
       <c r="P69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="3"/>
@@ -4215,34 +5300,50 @@
       <c r="AA69" s="3"/>
       <c r="AC69" s="2"/>
       <c r="AD69" s="3"/>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF69" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG69" t="str">
+        <f t="shared" si="6"/>
+        <v>overhead extension (sag)</v>
+      </c>
+      <c r="AH69" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI69" t="str">
+        <f t="shared" si="8"/>
+        <v>ez bar</v>
+      </c>
+    </row>
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="3"/>
@@ -4261,40 +5362,56 @@
       <c r="AA70" s="3"/>
       <c r="AC70" s="2"/>
       <c r="AD70" s="3"/>
-    </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF70" t="str">
+        <f t="shared" si="5"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG70" t="str">
+        <f t="shared" si="6"/>
+        <v>overhead extension (sag)</v>
+      </c>
+      <c r="AH70" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI70" t="str">
+        <f t="shared" si="8"/>
+        <v>1rope</v>
+      </c>
+    </row>
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B71" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" t="s">
+        <v>35</v>
+      </c>
+      <c r="F71" t="s">
+        <v>50</v>
+      </c>
+      <c r="G71" t="s">
         <v>141</v>
       </c>
-      <c r="C71" t="s">
-        <v>42</v>
-      </c>
-      <c r="D71" t="s">
-        <v>43</v>
-      </c>
-      <c r="E71" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" t="s">
-        <v>51</v>
-      </c>
-      <c r="G71" t="s">
-        <v>142</v>
-      </c>
       <c r="J71" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M71" t="s">
+        <v>46</v>
+      </c>
+      <c r="N71" t="s">
         <v>47</v>
       </c>
-      <c r="N71" t="s">
-        <v>48</v>
-      </c>
       <c r="P71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q71" s="2">
         <v>90</v>
@@ -4314,34 +5431,50 @@
       <c r="AA71" s="3"/>
       <c r="AC71" s="2"/>
       <c r="AD71" s="3"/>
-    </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF71" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG71" t="str">
+        <f t="shared" si="6"/>
+        <v>press</v>
+      </c>
+      <c r="AH71" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI71" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72" t="s">
         <v>35</v>
       </c>
-      <c r="E72" t="s">
-        <v>36</v>
-      </c>
       <c r="F72" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q72" s="2">
         <v>90</v>
@@ -4361,40 +5494,56 @@
       <c r="AA72" s="5"/>
       <c r="AC72" s="2"/>
       <c r="AD72" s="3"/>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF72" t="str">
+        <f t="shared" si="5"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG72" t="str">
+        <f t="shared" si="6"/>
+        <v>press</v>
+      </c>
+      <c r="AH72" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI72" t="str">
+        <f t="shared" si="8"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B73" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" t="s">
+        <v>42</v>
+      </c>
+      <c r="E73" t="s">
+        <v>35</v>
+      </c>
+      <c r="F73" t="s">
+        <v>50</v>
+      </c>
+      <c r="G73" t="s">
         <v>144</v>
       </c>
-      <c r="C73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" t="s">
-        <v>43</v>
-      </c>
-      <c r="E73" t="s">
-        <v>36</v>
-      </c>
-      <c r="F73" t="s">
-        <v>51</v>
-      </c>
-      <c r="G73" t="s">
-        <v>145</v>
-      </c>
       <c r="J73" t="s">
+        <v>45</v>
+      </c>
+      <c r="M73" t="s">
         <v>46</v>
       </c>
-      <c r="M73" t="s">
-        <v>47</v>
-      </c>
       <c r="O73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q73" s="2">
         <v>45</v>
@@ -4414,40 +5563,56 @@
       <c r="AA73" s="3"/>
       <c r="AC73" s="2"/>
       <c r="AD73" s="3"/>
-    </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF73" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG73" t="str">
+        <f t="shared" si="6"/>
+        <v>press (sag/s-t/trans)</v>
+      </c>
+      <c r="AH73" t="str">
+        <f t="shared" si="7"/>
+        <v>chest</v>
+      </c>
+      <c r="AI73" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" t="s">
         <v>35</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>36</v>
       </c>
-      <c r="F74" t="s">
-        <v>37</v>
-      </c>
       <c r="G74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q74" s="2">
         <v>45</v>
@@ -4467,28 +5632,44 @@
       <c r="AA74" s="3"/>
       <c r="AC74" s="2"/>
       <c r="AD74" s="3"/>
-    </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF74" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG74" t="str">
+        <f t="shared" si="6"/>
+        <v>press (trans)</v>
+      </c>
+      <c r="AH74" t="str">
+        <f t="shared" si="7"/>
+        <v>chest</v>
+      </c>
+      <c r="AI74" t="str">
+        <f t="shared" si="8"/>
+        <v>barbell</v>
+      </c>
+    </row>
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F75" t="s">
+        <v>95</v>
+      </c>
+      <c r="I75" t="s">
         <v>67</v>
       </c>
-      <c r="D75" t="s">
-        <v>93</v>
-      </c>
-      <c r="F75" t="s">
-        <v>96</v>
-      </c>
-      <c r="I75" t="s">
-        <v>68</v>
-      </c>
       <c r="P75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q75" s="2">
         <v>160</v>
@@ -4508,34 +5689,50 @@
       <c r="AA75" s="3"/>
       <c r="AC75" s="2"/>
       <c r="AD75" s="3"/>
-    </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF75" t="str">
+        <f t="shared" si="5"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG75" t="str">
+        <f t="shared" si="6"/>
+        <v>pull</v>
+      </c>
+      <c r="AH75" t="str">
+        <f t="shared" si="7"/>
+        <v>lat</v>
+      </c>
+      <c r="AI75" t="str">
+        <f t="shared" si="8"/>
+        <v>d-handle var</v>
+      </c>
+    </row>
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" t="s">
+        <v>35</v>
+      </c>
+      <c r="F76" t="s">
+        <v>60</v>
+      </c>
+      <c r="G76" t="s">
         <v>147</v>
       </c>
-      <c r="C76" t="s">
-        <v>67</v>
-      </c>
-      <c r="D76" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" t="s">
-        <v>61</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>148</v>
       </c>
-      <c r="H76" t="s">
-        <v>149</v>
-      </c>
       <c r="P76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q76" s="2">
         <v>160</v>
@@ -4555,34 +5752,50 @@
       <c r="AA76" s="3"/>
       <c r="AC76" s="2"/>
       <c r="AD76" s="3"/>
-    </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF76" t="str">
+        <f t="shared" si="5"/>
+        <v>Lat pull</v>
+      </c>
+      <c r="AG76" t="str">
+        <f t="shared" si="6"/>
+        <v>pull</v>
+      </c>
+      <c r="AH76" t="str">
+        <f t="shared" si="7"/>
+        <v>lat</v>
+      </c>
+      <c r="AI76" t="str">
+        <f t="shared" si="8"/>
+        <v>long light bend</v>
+      </c>
+    </row>
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" t="s">
+        <v>60</v>
+      </c>
+      <c r="G77" t="s">
         <v>147</v>
       </c>
-      <c r="C77" t="s">
-        <v>67</v>
-      </c>
-      <c r="D77" t="s">
-        <v>90</v>
-      </c>
-      <c r="E77" t="s">
-        <v>36</v>
-      </c>
-      <c r="F77" t="s">
-        <v>61</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>148</v>
       </c>
-      <c r="H77" t="s">
-        <v>149</v>
-      </c>
       <c r="P77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q77" s="2">
         <v>160</v>
@@ -4602,37 +5815,53 @@
       <c r="AA77" s="5"/>
       <c r="AC77" s="2"/>
       <c r="AD77" s="3"/>
-    </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF77" t="str">
+        <f t="shared" si="5"/>
+        <v>Lat pull2</v>
+      </c>
+      <c r="AG77" t="str">
+        <f t="shared" si="6"/>
+        <v>pull</v>
+      </c>
+      <c r="AH77" t="str">
+        <f t="shared" si="7"/>
+        <v>lat</v>
+      </c>
+      <c r="AI77" t="str">
+        <f t="shared" si="8"/>
+        <v>long light bend</v>
+      </c>
+    </row>
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" s="3"/>
@@ -4651,37 +5880,53 @@
       <c r="AA78" s="3"/>
       <c r="AC78" s="2"/>
       <c r="AD78" s="3"/>
-    </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF78" t="str">
+        <f t="shared" si="5"/>
+        <v>Free + Cable</v>
+      </c>
+      <c r="AG78" t="str">
+        <f t="shared" si="6"/>
+        <v>pushdown</v>
+      </c>
+      <c r="AH78" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI78" t="str">
+        <f t="shared" si="8"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G79" t="s">
+        <v>66</v>
+      </c>
+      <c r="I79" t="s">
         <v>67</v>
       </c>
-      <c r="I79" t="s">
-        <v>68</v>
-      </c>
       <c r="M79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" s="3"/>
@@ -4700,34 +5945,50 @@
       <c r="AA79" s="3"/>
       <c r="AC79" s="2"/>
       <c r="AD79" s="3"/>
-    </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF79" t="str">
+        <f t="shared" si="5"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG79" t="str">
+        <f t="shared" si="6"/>
+        <v>pushdown</v>
+      </c>
+      <c r="AH79" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI79" t="str">
+        <f t="shared" si="8"/>
+        <v>EZ bend</v>
+      </c>
+    </row>
+    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G80" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q80" s="2">
         <v>90</v>
@@ -4747,31 +6008,47 @@
       <c r="AA80" s="3"/>
       <c r="AC80" s="2"/>
       <c r="AD80" s="3"/>
-    </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF80" t="str">
+        <f t="shared" si="5"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG80" t="str">
+        <f t="shared" si="6"/>
+        <v>rear pull</v>
+      </c>
+      <c r="AH80" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI80" t="str">
+        <f t="shared" si="8"/>
+        <v>nooses</v>
+      </c>
+    </row>
+    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q81" s="2">
         <v>90</v>
@@ -4791,37 +6068,53 @@
       <c r="AA81" s="3"/>
       <c r="AC81" s="2"/>
       <c r="AD81" s="3"/>
-    </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF81" t="str">
+        <f t="shared" si="5"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG81" t="str">
+        <f t="shared" si="6"/>
+        <v>rear pull</v>
+      </c>
+      <c r="AH81" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI81" t="str">
+        <f t="shared" si="8"/>
+        <v>cuff</v>
+      </c>
+    </row>
+    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C82" t="s">
+        <v>41</v>
+      </c>
+      <c r="D82" t="s">
         <v>42</v>
       </c>
-      <c r="D82" t="s">
-        <v>43</v>
-      </c>
       <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" t="s">
         <v>36</v>
       </c>
-      <c r="F82" t="s">
-        <v>37</v>
-      </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q82" s="2">
         <v>30</v>
@@ -4840,40 +6133,56 @@
       <c r="AA82" s="5"/>
       <c r="AC82" s="2"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF82" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG82" t="str">
+        <f t="shared" si="6"/>
+        <v>rear raise (t-l)</v>
+      </c>
+      <c r="AH82" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI82" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
+        <v>41</v>
+      </c>
+      <c r="D83" t="s">
         <v>42</v>
       </c>
-      <c r="D83" t="s">
-        <v>43</v>
-      </c>
       <c r="E83" t="s">
+        <v>35</v>
+      </c>
+      <c r="F83" t="s">
         <v>36</v>
       </c>
-      <c r="F83" t="s">
-        <v>37</v>
-      </c>
       <c r="G83" t="s">
+        <v>108</v>
+      </c>
+      <c r="J83" t="s">
         <v>109</v>
       </c>
-      <c r="J83" t="s">
-        <v>110</v>
-      </c>
       <c r="N83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q83" s="2">
         <v>30</v>
@@ -4892,34 +6201,50 @@
       <c r="AA83" s="3"/>
       <c r="AC83" s="2"/>
       <c r="AD83" s="3"/>
-    </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF83" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG83" t="str">
+        <f t="shared" si="6"/>
+        <v>rear raise (trans/t-l)</v>
+      </c>
+      <c r="AH83" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI83" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B84" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" t="s">
+        <v>51</v>
+      </c>
+      <c r="I84" t="s">
         <v>154</v>
       </c>
-      <c r="C84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" t="s">
-        <v>139</v>
-      </c>
-      <c r="F84" t="s">
-        <v>51</v>
-      </c>
-      <c r="G84" t="s">
-        <v>52</v>
-      </c>
-      <c r="I84" t="s">
-        <v>155</v>
-      </c>
       <c r="M84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q84" s="2">
         <v>30</v>
@@ -4938,34 +6263,50 @@
       <c r="AA84" s="3"/>
       <c r="AC84" s="2"/>
       <c r="AD84" s="3"/>
-    </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF84" t="str">
+        <f t="shared" si="5"/>
+        <v>cable + bench</v>
+      </c>
+      <c r="AG84" t="str">
+        <f t="shared" si="6"/>
+        <v>rev fly</v>
+      </c>
+      <c r="AH84" t="str">
+        <f t="shared" si="7"/>
+        <v>shoulder</v>
+      </c>
+      <c r="AI84" t="str">
+        <f t="shared" si="8"/>
+        <v>1rope</v>
+      </c>
+    </row>
+    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q85" s="2">
         <v>30</v>
@@ -4985,34 +6326,50 @@
       <c r="AA85" s="3"/>
       <c r="AC85" s="2"/>
       <c r="AD85" s="3"/>
-    </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF85" t="str">
+        <f t="shared" si="5"/>
+        <v>lat row 2</v>
+      </c>
+      <c r="AG85" t="str">
+        <f t="shared" si="6"/>
+        <v>row</v>
+      </c>
+      <c r="AH85" t="str">
+        <f t="shared" si="7"/>
+        <v>back</v>
+      </c>
+      <c r="AI85" t="str">
+        <f t="shared" si="8"/>
+        <v>d-handle fix</v>
+      </c>
+    </row>
+    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" t="s">
+        <v>155</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" t="s">
         <v>156</v>
       </c>
-      <c r="C86" t="s">
-        <v>67</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>35</v>
+      </c>
+      <c r="F86" t="s">
         <v>157</v>
       </c>
-      <c r="E86" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" t="s">
-        <v>158</v>
-      </c>
       <c r="G86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P86" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q86" s="2">
         <v>30</v>
@@ -5032,34 +6389,50 @@
       <c r="AA86" s="3"/>
       <c r="AC86" s="2"/>
       <c r="AD86" s="3"/>
-    </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF86" t="str">
+        <f t="shared" si="5"/>
+        <v>lat row</v>
+      </c>
+      <c r="AG86" t="str">
+        <f t="shared" si="6"/>
+        <v>row</v>
+      </c>
+      <c r="AH86" t="str">
+        <f t="shared" si="7"/>
+        <v>lat</v>
+      </c>
+      <c r="AI86" t="str">
+        <f t="shared" si="8"/>
+        <v>mag close n-s</v>
+      </c>
+    </row>
+    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F87" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>47</v>
+      </c>
+      <c r="P87" t="s">
         <v>38</v>
-      </c>
-      <c r="N87" t="s">
-        <v>48</v>
-      </c>
-      <c r="P87" t="s">
-        <v>39</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" s="3"/>
@@ -5071,31 +6444,47 @@
       <c r="AA87" s="5"/>
       <c r="AC87" s="2"/>
       <c r="AD87" s="3"/>
-    </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF87" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG87" t="str">
+        <f t="shared" si="6"/>
+        <v>shrugg</v>
+      </c>
+      <c r="AH87" t="str">
+        <f t="shared" si="7"/>
+        <v>back</v>
+      </c>
+      <c r="AI87" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H88" t="s">
+        <v>37</v>
+      </c>
+      <c r="P88" t="s">
         <v>38</v>
-      </c>
-      <c r="P88" t="s">
-        <v>39</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" s="3"/>
@@ -5107,43 +6496,59 @@
       <c r="AA88" s="3"/>
       <c r="AC88" s="2"/>
       <c r="AD88" s="3"/>
-    </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF88" t="str">
+        <f t="shared" si="5"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG88" t="str">
+        <f t="shared" si="6"/>
+        <v>shrugg</v>
+      </c>
+      <c r="AH88" t="str">
+        <f t="shared" si="7"/>
+        <v>back</v>
+      </c>
+      <c r="AI88" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B89" t="s">
+        <v>159</v>
+      </c>
+      <c r="C89" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" t="s">
         <v>160</v>
       </c>
-      <c r="C89" t="s">
-        <v>94</v>
-      </c>
-      <c r="D89" t="s">
-        <v>161</v>
-      </c>
       <c r="E89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" t="s">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" t="s">
+        <v>84</v>
+      </c>
+      <c r="J89" t="s">
+        <v>109</v>
+      </c>
+      <c r="M89" t="s">
+        <v>46</v>
+      </c>
+      <c r="O89" t="s">
         <v>77</v>
       </c>
-      <c r="G89" t="s">
-        <v>64</v>
-      </c>
-      <c r="H89" t="s">
-        <v>85</v>
-      </c>
-      <c r="J89" t="s">
-        <v>110</v>
-      </c>
-      <c r="M89" t="s">
-        <v>47</v>
-      </c>
-      <c r="O89" t="s">
-        <v>78</v>
-      </c>
       <c r="P89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" s="3"/>
@@ -5162,43 +6567,59 @@
       <c r="AA89" s="3"/>
       <c r="AC89" s="2"/>
       <c r="AD89" s="3"/>
-    </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF89" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG89" t="str">
+        <f t="shared" si="6"/>
+        <v>skull crusher (s-t)</v>
+      </c>
+      <c r="AH89" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI89" t="str">
+        <f t="shared" si="8"/>
+        <v>nose bar</v>
+      </c>
+    </row>
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D90" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E90" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F90" t="s">
+        <v>76</v>
+      </c>
+      <c r="G90" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" t="s">
+        <v>84</v>
+      </c>
+      <c r="J90" t="s">
+        <v>109</v>
+      </c>
+      <c r="M90" t="s">
+        <v>46</v>
+      </c>
+      <c r="O90" t="s">
         <v>77</v>
       </c>
-      <c r="G90" t="s">
-        <v>28</v>
-      </c>
-      <c r="H90" t="s">
-        <v>85</v>
-      </c>
-      <c r="J90" t="s">
-        <v>110</v>
-      </c>
-      <c r="M90" t="s">
-        <v>47</v>
-      </c>
-      <c r="O90" t="s">
-        <v>78</v>
-      </c>
       <c r="P90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="3"/>
@@ -5217,37 +6638,53 @@
       <c r="AA90" s="3"/>
       <c r="AC90" s="2"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF90" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG90" t="str">
+        <f t="shared" si="6"/>
+        <v>skull crusher (sag)</v>
+      </c>
+      <c r="AH90" t="str">
+        <f t="shared" si="7"/>
+        <v>triceps</v>
+      </c>
+      <c r="AI90" t="str">
+        <f t="shared" si="8"/>
+        <v>nose bar</v>
+      </c>
+    </row>
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F91" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" t="s">
         <v>27</v>
       </c>
-      <c r="G91" t="s">
-        <v>28</v>
-      </c>
       <c r="J91" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N91" t="s">
+        <v>29</v>
+      </c>
+      <c r="P91" t="s">
         <v>30</v>
-      </c>
-      <c r="P91" t="s">
-        <v>31</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" s="3"/>
@@ -5266,22 +6703,38 @@
       <c r="AA91" s="3"/>
       <c r="AC91" s="2"/>
       <c r="AD91" s="3"/>
-    </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AF91" t="str">
+        <f t="shared" si="5"/>
+        <v>Bench + Freeweight</v>
+      </c>
+      <c r="AG91" t="str">
+        <f t="shared" si="6"/>
+        <v>spider curl</v>
+      </c>
+      <c r="AH91" t="str">
+        <f t="shared" si="7"/>
+        <v>biceps</v>
+      </c>
+      <c r="AI91" t="str">
+        <f t="shared" si="8"/>
+        <v>dumbell</v>
+      </c>
+    </row>
+    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" t="s">
         <v>34</v>
       </c>
-      <c r="D92" t="s">
-        <v>35</v>
-      </c>
       <c r="P92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" s="3"/>
@@ -5293,6 +6746,22 @@
       <c r="AA92" s="5"/>
       <c r="AC92" s="2"/>
       <c r="AD92" s="3"/>
+      <c r="AF92" t="str">
+        <f t="shared" si="5"/>
+        <v>free + freeweight</v>
+      </c>
+      <c r="AG92" t="str">
+        <f t="shared" si="6"/>
+        <v>squat</v>
+      </c>
+      <c r="AH92" t="str">
+        <f t="shared" si="7"/>
+        <v>legs</v>
+      </c>
+      <c r="AI92" t="str">
+        <f t="shared" si="8"/>
+        <v>barbell</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BA7A32-0453-4F24-93FB-9FDF46E14124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977763D3-6EBC-40A4-948E-75F58F4B3160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,19 +554,19 @@
     <t>elv_angle_world_fix</t>
   </si>
   <si>
-    <t>shoulder elv</t>
-  </si>
-  <si>
-    <t>elbow flex</t>
-  </si>
-  <si>
-    <t>angle (plane)</t>
-  </si>
-  <si>
     <t xml:space="preserve">angle (world) </t>
   </si>
   <si>
     <t>rot shoulder</t>
+  </si>
+  <si>
+    <t>shoulder (OA:OK)</t>
+  </si>
+  <si>
+    <t>elbow (OA:UA)</t>
+  </si>
+  <si>
+    <t>angle (OA : S)</t>
   </si>
 </sst>
 </file>
@@ -620,7 +620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -643,11 +643,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -665,6 +674,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -976,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI92"/>
+  <dimension ref="A1:AJ92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -1000,31 +1018,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9" t="s">
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2904,42 +2922,44 @@
       <c r="P32" t="s">
         <v>30</v>
       </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="3"/>
-      <c r="S32">
+      <c r="Q32" s="9"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="11">
         <v>10</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T32" s="9">
         <v>145</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="10">
         <v>0</v>
       </c>
-      <c r="W32" s="2"/>
-      <c r="X32" s="3"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="3"/>
-      <c r="AB32">
+      <c r="V32" s="11"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="10"/>
+      <c r="AB32" s="11">
         <v>0</v>
       </c>
-      <c r="AC32" s="2"/>
-      <c r="AD32" s="3"/>
-      <c r="AE32">
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="11">
         <v>0</v>
       </c>
-      <c r="AF32" t="str">
+      <c r="AF32" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Lat pull2</v>
       </c>
-      <c r="AG32" t="str">
+      <c r="AG32" s="11" t="str">
         <f t="shared" si="2"/>
         <v>extension</v>
       </c>
-      <c r="AH32" t="str">
+      <c r="AH32" s="11" t="str">
         <f t="shared" si="3"/>
         <v>triceps</v>
       </c>
-      <c r="AI32" t="str">
+      <c r="AI32" s="11" t="str">
         <f t="shared" si="4"/>
         <v>cuff</v>
       </c>
@@ -2978,9 +2998,10 @@
       <c r="P33" t="s">
         <v>30</v>
       </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="3"/>
-      <c r="S33">
+      <c r="Q33" s="2">
+        <v>30</v>
+      </c>
+      <c r="R33" s="3">
         <v>20</v>
       </c>
       <c r="T33" s="2">
@@ -2989,8 +3010,12 @@
       <c r="U33" s="3">
         <v>5</v>
       </c>
-      <c r="W33" s="2"/>
-      <c r="X33" s="3"/>
+      <c r="W33" s="2">
+        <v>70</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
       <c r="Z33" s="2"/>
       <c r="AA33" s="3"/>
       <c r="AB33">
@@ -3052,9 +3077,10 @@
       <c r="P34" t="s">
         <v>30</v>
       </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="3"/>
-      <c r="S34">
+      <c r="Q34" s="2">
+        <v>30</v>
+      </c>
+      <c r="R34" s="3">
         <v>20</v>
       </c>
       <c r="T34" s="2">
@@ -3063,10 +3089,11 @@
       <c r="U34" s="3">
         <v>5</v>
       </c>
-      <c r="W34" s="2"/>
-      <c r="X34" s="3"/>
-      <c r="Y34">
-        <v>0</v>
+      <c r="W34" s="2">
+        <v>80</v>
+      </c>
+      <c r="X34" s="3">
+        <v>10</v>
       </c>
       <c r="Z34" s="2"/>
       <c r="AA34" s="3"/>
@@ -3126,9 +3153,10 @@
       <c r="P35" t="s">
         <v>30</v>
       </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="3"/>
-      <c r="S35">
+      <c r="Q35" s="2">
+        <v>30</v>
+      </c>
+      <c r="R35" s="3">
         <v>20</v>
       </c>
       <c r="T35" s="2">
@@ -3137,10 +3165,11 @@
       <c r="U35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="2"/>
-      <c r="X35" s="3"/>
-      <c r="Y35">
-        <v>0</v>
+      <c r="W35" s="2">
+        <v>80</v>
+      </c>
+      <c r="X35" s="3">
+        <v>10</v>
       </c>
       <c r="Z35" s="2"/>
       <c r="AA35" s="3"/>
@@ -3200,10 +3229,11 @@
       <c r="P36" t="s">
         <v>30</v>
       </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="3"/>
-      <c r="S36">
+      <c r="Q36" s="2">
         <v>20</v>
+      </c>
+      <c r="R36" s="3">
+        <v>10</v>
       </c>
       <c r="T36" s="2">
         <v>100</v>
@@ -3213,12 +3243,16 @@
       </c>
       <c r="W36" s="2"/>
       <c r="X36" s="3"/>
+      <c r="Y36">
+        <v>0</v>
+      </c>
       <c r="Z36" s="2"/>
       <c r="AA36" s="3"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="3"/>
-      <c r="AE36">
+      <c r="AC36" s="2">
         <v>0</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>-30</v>
       </c>
       <c r="AF36" t="str">
         <f t="shared" si="1"/>
@@ -3268,36 +3302,48 @@
       <c r="P37" t="s">
         <v>30</v>
       </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="3"/>
-      <c r="S37">
+      <c r="Q37" s="9">
         <v>20</v>
       </c>
-      <c r="T37" s="2">
+      <c r="R37" s="10">
+        <v>10</v>
+      </c>
+      <c r="S37" s="11"/>
+      <c r="T37" s="9">
         <v>100</v>
       </c>
-      <c r="U37" s="3">
+      <c r="U37" s="10">
         <v>5</v>
       </c>
-      <c r="W37" s="2"/>
-      <c r="X37" s="3"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="5"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="3"/>
-      <c r="AF37" t="str">
+      <c r="V37" s="11"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="11"/>
+      <c r="AC37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="10">
+        <v>-30</v>
+      </c>
+      <c r="AE37" s="11"/>
+      <c r="AF37" s="11" t="str">
         <f t="shared" si="1"/>
         <v>cable + bench</v>
       </c>
-      <c r="AG37" t="str">
+      <c r="AG37" s="11" t="str">
         <f t="shared" si="2"/>
         <v>extension (sag)</v>
       </c>
-      <c r="AH37" t="str">
+      <c r="AH37" s="11" t="str">
         <f t="shared" si="3"/>
         <v>triceps</v>
       </c>
-      <c r="AI37" t="str">
+      <c r="AI37" s="11" t="str">
         <f t="shared" si="4"/>
         <v>cuff</v>
       </c>
@@ -3333,24 +3379,31 @@
       <c r="P38" t="s">
         <v>53</v>
       </c>
-      <c r="Q38" s="2">
-        <v>0</v>
-      </c>
-      <c r="R38" s="3">
+      <c r="Q38" s="2"/>
+      <c r="R38" s="3"/>
+      <c r="S38">
         <v>90</v>
       </c>
       <c r="T38" s="2">
         <v>0</v>
       </c>
       <c r="U38" s="3">
+        <v>45</v>
+      </c>
+      <c r="W38" s="2">
+        <v>10</v>
+      </c>
+      <c r="X38" s="3">
         <v>90</v>
       </c>
-      <c r="W38" s="2"/>
-      <c r="X38" s="3"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="3"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="3"/>
+      <c r="AC38" s="2">
+        <v>-90</v>
+      </c>
+      <c r="AD38" s="3">
+        <v>90</v>
+      </c>
       <c r="AF38" t="str">
         <f t="shared" si="1"/>
         <v>Free + Cable</v>
@@ -3393,24 +3446,31 @@
       <c r="P39" t="s">
         <v>53</v>
       </c>
-      <c r="Q39" s="2">
-        <v>0</v>
-      </c>
-      <c r="R39" s="3">
+      <c r="Q39" s="2"/>
+      <c r="R39" s="3"/>
+      <c r="S39">
         <v>90</v>
       </c>
       <c r="T39" s="2">
         <v>0</v>
       </c>
       <c r="U39" s="3">
+        <v>45</v>
+      </c>
+      <c r="W39" s="2">
+        <v>10</v>
+      </c>
+      <c r="X39" s="3">
         <v>90</v>
       </c>
-      <c r="W39" s="2"/>
-      <c r="X39" s="3"/>
       <c r="Z39" s="2"/>
       <c r="AA39" s="3"/>
-      <c r="AC39" s="2"/>
-      <c r="AD39" s="3"/>
+      <c r="AC39" s="2">
+        <v>-90</v>
+      </c>
+      <c r="AD39" s="3">
+        <v>90</v>
+      </c>
       <c r="AF39" t="str">
         <f t="shared" si="1"/>
         <v>lat row</v>
@@ -3453,24 +3513,31 @@
       <c r="P40" t="s">
         <v>53</v>
       </c>
-      <c r="Q40" s="2">
-        <v>0</v>
-      </c>
-      <c r="R40" s="3">
+      <c r="Q40" s="2"/>
+      <c r="R40" s="3"/>
+      <c r="S40">
         <v>90</v>
       </c>
       <c r="T40" s="2">
         <v>0</v>
       </c>
       <c r="U40" s="3">
+        <v>45</v>
+      </c>
+      <c r="W40" s="2">
+        <v>10</v>
+      </c>
+      <c r="X40" s="3">
         <v>90</v>
       </c>
-      <c r="W40" s="2"/>
-      <c r="X40" s="3"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="3"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="3"/>
+      <c r="AC40" s="2">
+        <v>-90</v>
+      </c>
+      <c r="AD40" s="3">
+        <v>90</v>
+      </c>
       <c r="AF40" t="str">
         <f t="shared" si="1"/>
         <v>lat row 2</v>
@@ -3495,7 +3562,7 @@
       <c r="B41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D41" t="s">
@@ -3550,7 +3617,7 @@
       <c r="B42" t="s">
         <v>103</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D42" t="s">
@@ -3596,7 +3663,7 @@
       <c r="B43" t="s">
         <v>103</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D43" t="s">
@@ -3642,7 +3709,7 @@
       <c r="B44" t="s">
         <v>103</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D44" t="s">
@@ -3660,29 +3727,34 @@
       <c r="P44" t="s">
         <v>38</v>
       </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="3"/>
-      <c r="T44" s="2"/>
-      <c r="U44" s="3"/>
-      <c r="W44" s="2"/>
-      <c r="X44" s="3"/>
-      <c r="Z44" s="2"/>
-      <c r="AA44" s="3"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="3"/>
-      <c r="AF44" t="str">
+      <c r="Q44" s="9"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="11"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="10"/>
+      <c r="Y44" s="11"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="10"/>
+      <c r="AB44" s="11"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="10"/>
+      <c r="AE44" s="11"/>
+      <c r="AF44" s="11" t="str">
         <f t="shared" si="1"/>
         <v>free + freeweight</v>
       </c>
-      <c r="AG44" t="str">
+      <c r="AG44" s="11" t="str">
         <f t="shared" si="2"/>
         <v>flexion</v>
       </c>
-      <c r="AH44" t="str">
+      <c r="AH44" s="11" t="str">
         <f t="shared" si="3"/>
         <v>forearm</v>
       </c>
-      <c r="AI44" t="str">
+      <c r="AI44" s="11" t="str">
         <f t="shared" si="4"/>
         <v>barbell</v>
       </c>
@@ -3709,7 +3781,7 @@
       <c r="G45" t="s">
         <v>106</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="7" t="s">
         <v>107</v>
       </c>
       <c r="K45" t="s">
@@ -3774,7 +3846,7 @@
       <c r="G46" t="s">
         <v>108</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="7" t="s">
         <v>109</v>
       </c>
       <c r="M46" t="s">
@@ -3783,36 +3855,44 @@
       <c r="P46" t="s">
         <v>41</v>
       </c>
-      <c r="Q46" s="2">
-        <v>25</v>
-      </c>
-      <c r="R46" s="3">
+      <c r="Q46" s="9"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="11">
         <v>80</v>
       </c>
-      <c r="T46" s="2"/>
-      <c r="U46" s="3"/>
-      <c r="V46">
+      <c r="T46" s="9">
+        <v>90</v>
+      </c>
+      <c r="U46" s="10">
         <v>20</v>
       </c>
-      <c r="W46" s="2"/>
-      <c r="X46" s="3"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="3"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="3"/>
-      <c r="AF46" t="str">
+      <c r="V46" s="11"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="10"/>
+      <c r="AB46" s="11">
+        <v>90</v>
+      </c>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="10"/>
+      <c r="AE46" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Bench + Freeweight</v>
       </c>
-      <c r="AG46" t="str">
+      <c r="AG46" s="11" t="str">
         <f t="shared" si="2"/>
         <v>fly</v>
       </c>
-      <c r="AH46" t="str">
+      <c r="AH46" s="11" t="str">
         <f t="shared" si="3"/>
         <v>chest</v>
       </c>
-      <c r="AI46" t="str">
+      <c r="AI46" s="11" t="str">
         <f t="shared" si="4"/>
         <v>dumbell</v>
       </c>
@@ -3855,19 +3935,26 @@
         <v>25</v>
       </c>
       <c r="R47" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T47" s="2"/>
       <c r="U47" s="3"/>
       <c r="V47">
         <v>20</v>
       </c>
-      <c r="W47" s="2"/>
-      <c r="X47" s="3"/>
+      <c r="W47" s="2">
+        <v>-30</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
       <c r="Z47" s="4"/>
       <c r="AA47" s="5"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="3"/>
+      <c r="AE47">
+        <v>90</v>
+      </c>
       <c r="AF47" t="str">
         <f t="shared" si="1"/>
         <v>cable + bench</v>
@@ -3923,7 +4010,7 @@
         <v>25</v>
       </c>
       <c r="R48" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="3"/>
@@ -3936,6 +4023,9 @@
       <c r="AA48" s="3"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="3"/>
+      <c r="AE48">
+        <v>90</v>
+      </c>
       <c r="AF48" t="str">
         <f t="shared" si="1"/>
         <v>cable + bench</v>
@@ -3953,7 +4043,7 @@
         <v>d-handle fix</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -4021,7 +4111,7 @@
         <v>d-handle fix</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -4085,8 +4175,11 @@
         <f t="shared" si="4"/>
         <v>d-handle var</v>
       </c>
-    </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -4156,8 +4249,11 @@
         <f t="shared" si="4"/>
         <v>dumbell</v>
       </c>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -4222,7 +4318,7 @@
         <v>ropes</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -4284,7 +4380,7 @@
         <v>dumbell</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -4350,7 +4446,7 @@
         <v>nooses</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -4402,7 +4498,7 @@
         <v>plates</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -4463,7 +4559,7 @@
         <v>dumbell</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -4525,7 +4621,7 @@
         <v>cuff</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -4587,7 +4683,7 @@
         <v>d-handle var</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -4649,7 +4745,7 @@
         <v>dumbell</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>31</v>
       </c>
@@ -4708,7 +4804,7 @@
         <v>dumbell</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -4773,7 +4869,7 @@
         <v>dumbell</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -4841,7 +4937,7 @@
         <v>nooses</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -4912,7 +5008,7 @@
         <v>ez bar</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>54</v>
       </c>

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977763D3-6EBC-40A4-948E-75F58F4B3160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9056FD-EBAC-40A2-A6A4-71DDE22FEB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebungen" sheetId="1" r:id="rId1"/>

--- a/biomechanics/execution/exercise_kinematics.xlsx
+++ b/biomechanics/execution/exercise_kinematics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubis\Projekte\GYM_APP\biomechanics\execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9056FD-EBAC-40A2-A6A4-71DDE22FEB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DA4BA8-F4AC-44A3-A810-5AB87D087F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebungen" sheetId="1" r:id="rId1"/>
@@ -6868,5 +6868,6 @@
     <mergeCell ref="AC1:AE1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>